--- a/compare/output/dscale_per_capita_co2_downscaled_SSP434.xlsx
+++ b/compare/output/dscale_per_capita_co2_downscaled_SSP434.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5995818507458498</v>
+        <v>0.599110339175709</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79179497235969</v>
+        <v>0.7914087615561373</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6774568815458547</v>
+        <v>0.6772297796330579</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5750037022008844</v>
+        <v>0.5748790120750984</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4758384874918551</v>
+        <v>0.4757859508953396</v>
       </c>
       <c r="J2" t="n">
         <v>0.3714336774489853</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.07288663388359204</v>
+        <v>0.07288182463058926</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1336491348992125</v>
+        <v>0.1336213078294672</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1495906891993215</v>
+        <v>0.1495628481925907</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1553602936536136</v>
+        <v>0.1553378166342047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.144621059143854</v>
+        <v>0.1446100676136131</v>
       </c>
       <c r="J3" t="n">
         <v>0.1166658388205136</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.009055476293861008</v>
+        <v>0.009266381324566302</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01800712959085459</v>
+        <v>0.01815117136487689</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02382912505726877</v>
+        <v>0.02390533572126747</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02705971114285406</v>
+        <v>0.0270995512181518</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02569695199555923</v>
+        <v>0.02571265485968314</v>
       </c>
       <c r="J4" t="n">
         <v>0.0209251257772996</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.1636180957284898</v>
+        <v>0.1635111177073554</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1429883049198602</v>
+        <v>0.1429408677320643</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07018460460001348</v>
+        <v>0.07018022174414718</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03961855382307666</v>
+        <v>0.03962386239354441</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02497951417710699</v>
+        <v>0.02498347631615743</v>
       </c>
       <c r="J5" t="n">
         <v>0.01649902073234586</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0740686998490007</v>
+        <v>0.07404696591487729</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09631640993773403</v>
+        <v>0.09629968604519078</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1039878341189613</v>
+        <v>0.1039709323315441</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1082595364410537</v>
+        <v>0.1082458987570138</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09893876084646747</v>
+        <v>0.09893188831899646</v>
       </c>
       <c r="J6" t="n">
         <v>0.07970441381683328</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.02542308382011075</v>
+        <v>0.02550322618556384</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03087873730863336</v>
+        <v>0.03094889620568487</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02302589359156381</v>
+        <v>0.02307758557514566</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01691811492122221</v>
+        <v>0.01695251731351165</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01187383948697524</v>
+        <v>0.01189008893782337</v>
       </c>
       <c r="J7" t="n">
         <v>0.007863666649948576</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.09534909192540014</v>
+        <v>0.09530981294645217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1248191626701307</v>
+        <v>0.1247877808418494</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1043230805141026</v>
+        <v>0.1043077953843366</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08541687968906783</v>
+        <v>0.08541044688073406</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06636621738200378</v>
+        <v>0.06636425902176392</v>
       </c>
       <c r="J8" t="n">
         <v>0.0483103914743688</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0008177531423687909</v>
+        <v>0.001604661869984021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0007741530212980554</v>
+        <v>0.001336704216774642</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000665064026933641</v>
+        <v>0.0009772665723282541</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0006175807533621442</v>
+        <v>0.0007831327035641175</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005380424723553778</v>
+        <v>0.0006047597389274446</v>
       </c>
       <c r="J9" t="n">
         <v>0.000406944222758104</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03866095056631735</v>
+        <v>0.03865337795474347</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06874009615891136</v>
+        <v>0.06872294017902016</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08651263941387985</v>
+        <v>0.08649264543099648</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09525585279951736</v>
+        <v>0.09523992566587239</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09149746411420248</v>
+        <v>0.09148925933091512</v>
       </c>
       <c r="J10" t="n">
         <v>0.0764586452936077</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.005597669883608266</v>
+        <v>0.005708088422840259</v>
       </c>
       <c r="F11" t="n">
-        <v>0.007888547342294079</v>
+        <v>0.007976536855380682</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007376860891317351</v>
+        <v>0.007432826936741961</v>
       </c>
       <c r="H11" t="n">
-        <v>0.006495520853913263</v>
+        <v>0.006528918092282863</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005360437630488382</v>
+        <v>0.00537490563977738</v>
       </c>
       <c r="J11" t="n">
         <v>0.004186335787341272</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.3330438334805285</v>
+        <v>0.3327959510295512</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4078420861371772</v>
+        <v>0.4076555784358954</v>
       </c>
       <c r="G12" t="n">
-        <v>0.321530778523975</v>
+        <v>0.3214318067689913</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2482863857854726</v>
+        <v>0.2482383469684543</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1869086708203855</v>
+        <v>0.186890696198305</v>
       </c>
       <c r="J12" t="n">
         <v>0.1305556380109922</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.02855720162531863</v>
+        <v>0.028569669131565</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04538267543345917</v>
+        <v>0.04538712641073618</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04990957150429751</v>
+        <v>0.04990861363275313</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05030646907795613</v>
+        <v>0.05030440536497611</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04474409631525213</v>
+        <v>0.04474284994497408</v>
       </c>
       <c r="J13" t="n">
         <v>0.03521210400859356</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.169519869611282</v>
+        <v>1.169550604245548</v>
       </c>
       <c r="F14" t="n">
-        <v>1.299218272801643</v>
+        <v>1.29927454639844</v>
       </c>
       <c r="G14" t="n">
-        <v>1.290675010219415</v>
+        <v>1.290754335747561</v>
       </c>
       <c r="H14" t="n">
-        <v>1.278172016201406</v>
+        <v>1.278275483413994</v>
       </c>
       <c r="I14" t="n">
-        <v>1.205062003017975</v>
+        <v>1.205183383456667</v>
       </c>
       <c r="J14" t="n">
-        <v>1.120442193784988</v>
+        <v>1.120575721495687</v>
       </c>
       <c r="K14" t="n">
-        <v>1.060694554512355</v>
+        <v>1.06083810997164</v>
       </c>
       <c r="L14" t="n">
-        <v>1.026514929107843</v>
+        <v>1.026668150128351</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01284772247064</v>
+        <v>1.013012388143635</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9971658320785175</v>
+        <v>0.997342402989506</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9662209170597758</v>
+        <v>0.9664085058965214</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9204670443592481</v>
+        <v>0.9206641841823983</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.864073815576623</v>
+        <v>0.8642794582465301</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7863340861777662</v>
+        <v>0.7865440766501219</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7133169277596628</v>
+        <v>0.7135334648458248</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6212782840559844</v>
+        <v>0.6214964179775763</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5049620358567891</v>
+        <v>0.5051722139145566</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3859514572758566</v>
+        <v>0.3861494116887866</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7350651813588518</v>
+        <v>0.7350577142492433</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8958018405434151</v>
+        <v>0.8957952768872467</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9270926535241555</v>
+        <v>0.9270926026913722</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9284280687099035</v>
+        <v>0.9284342558021067</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8701469334480131</v>
+        <v>0.8701560342681243</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7986829290229738</v>
+        <v>0.7986921159479879</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7470789478894968</v>
+        <v>0.7470873812622518</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7174737517280891</v>
+        <v>0.7174813668850983</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7043662510456918</v>
+        <v>0.7043729523253086</v>
       </c>
       <c r="N15" t="n">
-        <v>0.689992809346608</v>
+        <v>0.6899981557880326</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6644916417366316</v>
+        <v>0.6644953589031499</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6288388041789561</v>
+        <v>0.6288409705214268</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.586570689786014</v>
+        <v>0.5865716522695176</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5307166953973289</v>
+        <v>0.5307166858943535</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4788441740115852</v>
+        <v>0.478843193708809</v>
       </c>
       <c r="T15" t="n">
-        <v>0.414827474719995</v>
+        <v>0.4148252414815913</v>
       </c>
       <c r="U15" t="n">
-        <v>0.33527239161224</v>
+        <v>0.3352686672732521</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2547155579063075</v>
+        <v>0.2547103413498819</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.134265841247807</v>
+        <v>2.134399956572181</v>
       </c>
       <c r="F16" t="n">
-        <v>2.072579229069776</v>
+        <v>2.07280651011251</v>
       </c>
       <c r="G16" t="n">
-        <v>1.748906862623198</v>
+        <v>1.749155667943203</v>
       </c>
       <c r="H16" t="n">
-        <v>1.521346384725007</v>
+        <v>1.521592485990751</v>
       </c>
       <c r="I16" t="n">
-        <v>1.304111472697034</v>
+        <v>1.304336109073682</v>
       </c>
       <c r="J16" t="n">
-        <v>1.134252602203008</v>
+        <v>1.134454678726394</v>
       </c>
       <c r="K16" t="n">
-        <v>1.026712922829854</v>
+        <v>1.026900629771051</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9657161090693779</v>
+        <v>0.9658983482746262</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9359988929489943</v>
+        <v>0.9361831780740463</v>
       </c>
       <c r="N16" t="n">
-        <v>0.909265398904244</v>
+        <v>0.9094539322247918</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8689191133813672</v>
+        <v>0.8691093991675393</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8141995626120566</v>
+        <v>0.8143876247317992</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7502613498850247</v>
+        <v>0.7504438502523653</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6700890205229962</v>
+        <v>0.6702620245902668</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5974558270219724</v>
+        <v>0.5976219499318073</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5126242408635296</v>
+        <v>0.5127812545392691</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4114534158472933</v>
+        <v>0.4115965610156933</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3110176383095349</v>
+        <v>0.3111459750130605</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4938725766232003</v>
+        <v>0.4938290892611142</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5591579084371848</v>
+        <v>0.5590571268204025</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5462530025065391</v>
+        <v>0.5460973096177926</v>
       </c>
       <c r="H17" t="n">
-        <v>0.524403332026073</v>
+        <v>0.5241960138197166</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4759406224354699</v>
+        <v>0.4756998799083444</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4226867587688661</v>
+        <v>0.4224238112610628</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3824935695120751</v>
+        <v>0.382209219163929</v>
       </c>
       <c r="L17" t="n">
-        <v>0.357308166060359</v>
+        <v>0.3569994803076809</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3451767670109134</v>
+        <v>0.3448403720793964</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3368117292715563</v>
+        <v>0.3364504916778174</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3257737457329571</v>
+        <v>0.3253950253152539</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3107834790693371</v>
+        <v>0.310394235754999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2923095682518395</v>
+        <v>0.2919135669640847</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2667132257050311</v>
+        <v>0.2663189371629964</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2430367022415924</v>
+        <v>0.2426402814786079</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2133975647902011</v>
+        <v>0.2130090698948608</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1756053869939711</v>
+        <v>0.1752425012419148</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1362632706252111</v>
+        <v>0.1359330863470186</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7535711483832359</v>
+        <v>0.7535723342960513</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9218780350482089</v>
+        <v>0.9218913188823985</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9262007772342487</v>
+        <v>0.9262208205243291</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9105616545403507</v>
+        <v>0.9105862696552114</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8592332706374085</v>
+        <v>0.8592657053291536</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8184018283883991</v>
+        <v>0.81845204233987</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8046635122202005</v>
+        <v>0.8047379495651402</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8146981291905345</v>
+        <v>0.8148016258194893</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8344327788288893</v>
+        <v>0.8345652016583439</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8386014114618054</v>
+        <v>0.8387558729861205</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8146478793382369</v>
+        <v>0.8148134938815897</v>
       </c>
       <c r="P18" t="n">
-        <v>0.768070406332494</v>
+        <v>0.7682374418613509</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7086285673277039</v>
+        <v>0.7087910357310879</v>
       </c>
       <c r="R18" t="n">
-        <v>0.632346475985992</v>
+        <v>0.6324991960997439</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5627656791810828</v>
+        <v>0.5629103961047578</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4817115064602613</v>
+        <v>0.4818460420781021</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3855652653746238</v>
+        <v>0.3856856754436438</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2907164883546958</v>
+        <v>0.2908223242491718</v>
       </c>
     </row>
     <row r="19">
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0004734417781224688</v>
+        <v>0.0005175197467487402</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0006170936102477402</v>
+        <v>0.0006496874082810915</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0008520435390284189</v>
+        <v>0.0008794883740629368</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001249318614312058</v>
+        <v>0.001273317665055925</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001670298384482458</v>
+        <v>0.001685950053666656</v>
       </c>
       <c r="J19" t="n">
         <v>0.001903668829356958</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0001937287901399643</v>
+        <v>0.0002929673125400931</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001815387055648489</v>
+        <v>0.000260388850406147</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001822697646256932</v>
+        <v>0.0002579542614850105</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0001970328444032511</v>
+        <v>0.0002699261612788934</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000189541436961019</v>
+        <v>0.0002399980694853643</v>
       </c>
       <c r="J20" t="n">
         <v>0.0001371742112482853</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.008903229214353629</v>
+        <v>0.00890983202450963</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01618207613573661</v>
+        <v>0.01618630111057689</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0271089129429119</v>
+        <v>0.02711095264863948</v>
       </c>
       <c r="H21" t="n">
-        <v>0.04267326666158205</v>
+        <v>0.04267405701703256</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05662699566377147</v>
+        <v>0.05662661008414119</v>
       </c>
       <c r="J21" t="n">
         <v>0.06176914578457825</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.017825338102564</v>
+        <v>0.01783066421180289</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02153477599008619</v>
+        <v>0.02153905632436649</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02743688778793471</v>
+        <v>0.02744026486272504</v>
       </c>
       <c r="H22" t="n">
-        <v>0.03816833070415884</v>
+        <v>0.03817063508433036</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04921767384617965</v>
+        <v>0.04921838145417112</v>
       </c>
       <c r="J22" t="n">
         <v>0.05440577619791299</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.03180988757923219</v>
+        <v>0.03181465774626275</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03730068306326657</v>
+        <v>0.03730481360206094</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04408428683017225</v>
+        <v>0.04408761702581492</v>
       </c>
       <c r="H23" t="n">
-        <v>0.05497945404285227</v>
+        <v>0.05498187887837967</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06335904458205942</v>
+        <v>0.06336004627836953</v>
       </c>
       <c r="J23" t="n">
         <v>0.0636584428539501</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0004064782778573988</v>
+        <v>0.0004557728602615765</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0005049052503754833</v>
+        <v>0.000541748671475109</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0006213261498137955</v>
+        <v>0.0006540275261197848</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0008216513570814732</v>
+        <v>0.0008514333233067381</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001002579770545805</v>
+        <v>0.001023034160089269</v>
       </c>
       <c r="J24" t="n">
         <v>0.001057781662644563</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0008804784116959121</v>
+        <v>0.0009033787470673752</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001403577245535949</v>
+        <v>0.001420089919012842</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00206950688646257</v>
+        <v>0.002083202682646057</v>
       </c>
       <c r="H25" t="n">
-        <v>0.002985226296718548</v>
+        <v>0.002997058622912116</v>
       </c>
       <c r="I25" t="n">
-        <v>0.003786972004809454</v>
+        <v>0.003795086944819761</v>
       </c>
       <c r="J25" t="n">
         <v>0.004124681962362277</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.007577365390581158</v>
+        <v>0.007584025376670475</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01122839497389946</v>
+        <v>0.01123304846070858</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01778089095756536</v>
+        <v>0.0177841353416753</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02893139635405528</v>
+        <v>0.02893332200196519</v>
       </c>
       <c r="I26" t="n">
-        <v>0.04196447476123644</v>
+        <v>0.04196481681710854</v>
       </c>
       <c r="J26" t="n">
         <v>0.05091167121529647</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.002331353574277765</v>
+        <v>0.002341342179382205</v>
       </c>
       <c r="F27" t="n">
-        <v>0.003344263733741522</v>
+        <v>0.003351520664532342</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005175078770584389</v>
+        <v>0.005180780074867384</v>
       </c>
       <c r="H27" t="n">
-        <v>0.008280350257342325</v>
+        <v>0.008285021487659458</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01169402893685148</v>
+        <v>0.01169675446089881</v>
       </c>
       <c r="J27" t="n">
         <v>0.01372801703771668</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.746115029311445</v>
+        <v>1.745953140847663</v>
       </c>
       <c r="F28" t="n">
-        <v>2.397483399385143</v>
+        <v>2.397349923657372</v>
       </c>
       <c r="G28" t="n">
-        <v>2.383507260442719</v>
+        <v>2.383386091306133</v>
       </c>
       <c r="H28" t="n">
-        <v>2.243067615140179</v>
+        <v>2.242958187202667</v>
       </c>
       <c r="I28" t="n">
-        <v>1.862177221278797</v>
+        <v>1.862108565889495</v>
       </c>
       <c r="J28" t="n">
         <v>1.395878593047413</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.07145503445858557</v>
+        <v>0.07522996051385833</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1321153951541639</v>
+        <v>0.1333974113069509</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1504439137054762</v>
+        <v>0.150700984086912</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1453278257695419</v>
+        <v>0.1454201282924101</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1312074244560138</v>
+        <v>0.1312264924513888</v>
       </c>
       <c r="J29" t="n">
         <v>0.1178902042455575</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.1174673748920075</v>
+        <v>0.1135060028944347</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3298799623322764</v>
+        <v>0.3177293239257276</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5616080435885116</v>
+        <v>0.5454522402133962</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6954180207471277</v>
+        <v>0.6824312909920194</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7100568571944829</v>
+        <v>0.7032337228211769</v>
       </c>
       <c r="J30" t="n">
         <v>0.6646078943976186</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.1565528860757559</v>
+        <v>0.1481548554799065</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3026923584779676</v>
+        <v>0.2902998495013137</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3786479201086266</v>
+        <v>0.3673952516517549</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3857890374218284</v>
+        <v>0.3784909684202939</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3599901159433983</v>
+        <v>0.3565083260225753</v>
       </c>
       <c r="J31" t="n">
         <v>0.330655273243733</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.05841736924184481</v>
+        <v>0.06224897398553914</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1234392722023493</v>
+        <v>0.1239557821098801</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1644105576226872</v>
+        <v>0.1630748735117319</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1745814611497714</v>
+        <v>0.1732876779419811</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1640958675895564</v>
+        <v>0.1633977006022047</v>
       </c>
       <c r="J32" t="n">
         <v>0.1484164465458204</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.03222365783596338</v>
+        <v>0.03620452520509385</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05823128829918054</v>
+        <v>0.06083979704663587</v>
       </c>
       <c r="G33" t="n">
-        <v>0.06691442708341187</v>
+        <v>0.06840230912959748</v>
       </c>
       <c r="H33" t="n">
-        <v>0.06481298510666288</v>
+        <v>0.06566303392025037</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0584853558311865</v>
+        <v>0.05885795191558939</v>
       </c>
       <c r="J33" t="n">
         <v>0.05283450119635846</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.3713081507096305</v>
+        <v>0.3504479195946036</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2938728536124542</v>
+        <v>0.2822152185592929</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1503917105595053</v>
+        <v>0.146832786479909</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0840973117961113</v>
+        <v>0.0833417556118809</v>
       </c>
       <c r="I34" t="n">
-        <v>0.05393284314388697</v>
+        <v>0.05388689882620346</v>
       </c>
       <c r="J34" t="n">
         <v>0.04000742670745439</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02865211668031789</v>
+        <v>0.04440872337303293</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03530299214690828</v>
+        <v>0.05240988565663619</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02995762891439553</v>
+        <v>0.04454404162554824</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02278671483134477</v>
+        <v>0.03258517554170037</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01664157394902748</v>
+        <v>0.02127384544520143</v>
       </c>
       <c r="J35" t="n">
         <v>0.01215730675357663</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.02140578067110015</v>
+        <v>0.04141294904609967</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02416890347424431</v>
+        <v>0.04344939440213216</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02142822496091578</v>
+        <v>0.03442022902045066</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01821098512704714</v>
+        <v>0.02544462330435556</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01545982573232945</v>
+        <v>0.01849257909861167</v>
       </c>
       <c r="J36" t="n">
         <v>0.01314683077106246</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.0424726502334699</v>
+        <v>0.09455500697061385</v>
       </c>
       <c r="F37" t="n">
-        <v>0.03544237420881555</v>
+        <v>0.07687584524661874</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02486114124031032</v>
+        <v>0.05088028416300044</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01665991157322878</v>
+        <v>0.03103364621107458</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01060553263198263</v>
+        <v>0.01675571829448617</v>
       </c>
       <c r="J37" t="n">
         <v>0.006058445405364636</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.05072024100582329</v>
+        <v>0.0557868506371657</v>
       </c>
       <c r="F38" t="n">
-        <v>0.08792259894263872</v>
+        <v>0.09137991989293039</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1043270400190392</v>
+        <v>0.1060447957516483</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1045302500099093</v>
+        <v>0.1053722875212393</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09552723765523975</v>
+        <v>0.09586909255444553</v>
       </c>
       <c r="J38" t="n">
         <v>0.08484485320835428</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.1202634662390703</v>
+        <v>0.1168992357988297</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2621897236283228</v>
+        <v>0.2538740224225922</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3376608839924961</v>
+        <v>0.329203331712118</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3474090763248616</v>
+        <v>0.3417490589959702</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3209379722884446</v>
+        <v>0.3182440356952549</v>
       </c>
       <c r="J39" t="n">
         <v>0.2900304047748792</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.08287862856788426</v>
+        <v>0.08106318910211489</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1549623393885689</v>
+        <v>0.1509698584795017</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1827668895733916</v>
+        <v>0.1789828949678408</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1854274319691278</v>
+        <v>0.1828836358489931</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1731278988434308</v>
+        <v>0.1718825415097602</v>
       </c>
       <c r="J40" t="n">
         <v>0.1615741507267052</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.02942633663968227</v>
+        <v>0.03127691263336001</v>
       </c>
       <c r="F41" t="n">
-        <v>0.04648001723194013</v>
+        <v>0.04792453846222885</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05242496835197508</v>
+        <v>0.05323380704533879</v>
       </c>
       <c r="H41" t="n">
-        <v>0.05213827595325899</v>
+        <v>0.0525440340124786</v>
       </c>
       <c r="I41" t="n">
-        <v>0.04897068349804833</v>
+        <v>0.04911120338842288</v>
       </c>
       <c r="J41" t="n">
         <v>0.04597514313369246</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.0703248867980517</v>
+        <v>0.1596411308896363</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05799682624509895</v>
+        <v>0.1331057536577253</v>
       </c>
       <c r="G42" t="n">
-        <v>0.038093797834152</v>
+        <v>0.08783889239490907</v>
       </c>
       <c r="H42" t="n">
-        <v>0.02174965096806314</v>
+        <v>0.0500055705845284</v>
       </c>
       <c r="I42" t="n">
-        <v>0.009889026930215485</v>
+        <v>0.02212246600126695</v>
       </c>
       <c r="J42" t="n">
         <v>0.001070670839462827</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.3125585751571889</v>
+        <v>0.2979507119563893</v>
       </c>
       <c r="F43" t="n">
-        <v>0.410343975018004</v>
+        <v>0.3965905561398035</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3564576545239141</v>
+        <v>0.3486838426563936</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2809129866735032</v>
+        <v>0.2775952628529406</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2205407733539635</v>
+        <v>0.2194107259211567</v>
       </c>
       <c r="J43" t="n">
         <v>0.1807849915691268</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.0709285643530746</v>
+        <v>0.06953531157864509</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1281016641672835</v>
+        <v>0.125070283165408</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1457225016173495</v>
+        <v>0.1429822047758423</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1385781396072974</v>
+        <v>0.1369315602777264</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1226686783413869</v>
+        <v>0.1219328556524989</v>
       </c>
       <c r="J44" t="n">
         <v>0.1085498162603467</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.03561540951964438</v>
+        <v>0.04335900968458705</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05472047744920255</v>
+        <v>0.06169050177996818</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0583594652171665</v>
+        <v>0.06324625381854986</v>
       </c>
       <c r="H45" t="n">
-        <v>0.05521547147367942</v>
+        <v>0.05813573322374976</v>
       </c>
       <c r="I45" t="n">
-        <v>0.04945816728113751</v>
+        <v>0.05076275208329447</v>
       </c>
       <c r="J45" t="n">
         <v>0.04404566787395917</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2284732934915311</v>
+        <v>0.2168708168932541</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4582816689494596</v>
+        <v>0.4400300024212794</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5506005761142384</v>
+        <v>0.5346265264581131</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5341913195811027</v>
+        <v>0.5243450913868618</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4452464624611721</v>
+        <v>0.4410881548710833</v>
       </c>
       <c r="J46" t="n">
         <v>0.3571313616144062</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.02143435468895079</v>
+        <v>0.0292630274809795</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02894073801721463</v>
+        <v>0.03689758277330828</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02904578360924703</v>
+        <v>0.03484391941702741</v>
       </c>
       <c r="H47" t="n">
-        <v>0.02624570415953803</v>
+        <v>0.02976797982783794</v>
       </c>
       <c r="I47" t="n">
-        <v>0.02243289326205232</v>
+        <v>0.02404092955192335</v>
       </c>
       <c r="J47" t="n">
         <v>0.01889950042798045</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.04465912851975971</v>
+        <v>0.05108444893550788</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0801495969551824</v>
+        <v>0.08456907099860425</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0949232006272125</v>
+        <v>0.09734719692726601</v>
       </c>
       <c r="H48" t="n">
-        <v>0.09704802235407171</v>
+        <v>0.09823659343050653</v>
       </c>
       <c r="I48" t="n">
-        <v>0.09355880338075408</v>
+        <v>0.09396581643568593</v>
       </c>
       <c r="J48" t="n">
         <v>0.09017267648552565</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.07132552882240113</v>
+        <v>0.06932785516216484</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1209636446491872</v>
+        <v>0.1177884164490585</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1378670174740073</v>
+        <v>0.1350489154068643</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1380801628255056</v>
+        <v>0.1362237828194058</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1316054095408187</v>
+        <v>0.1306636601770069</v>
       </c>
       <c r="J49" t="n">
         <v>0.1248956948243141</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.03105554927027945</v>
+        <v>0.04023079533883924</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0476372802399413</v>
+        <v>0.05580017655254566</v>
       </c>
       <c r="G50" t="n">
-        <v>0.05414283059521956</v>
+        <v>0.059421505451952</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05533770310368186</v>
+        <v>0.05820476858345021</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05359175891252761</v>
+        <v>0.05474854715626701</v>
       </c>
       <c r="J50" t="n">
         <v>0.05092707045735476</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.04385424576191654</v>
+        <v>0.04304381918854964</v>
       </c>
       <c r="F51" t="n">
-        <v>0.09197081184398477</v>
+        <v>0.08946164384771244</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1189786034580947</v>
+        <v>0.1162607257883125</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1272145844804078</v>
+        <v>0.1252663553160043</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1236609315494123</v>
+        <v>0.1226619984265106</v>
       </c>
       <c r="J51" t="n">
         <v>0.1171575688161189</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.1593067234649175</v>
+        <v>0.1533103906511072</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3743339946592666</v>
+        <v>0.3608021716635461</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5325843008055902</v>
+        <v>0.5177707012095089</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5960628222741545</v>
+        <v>0.5852983883245171</v>
       </c>
       <c r="I52" t="n">
-        <v>0.58603712116047</v>
+        <v>0.5805768677700341</v>
       </c>
       <c r="J52" t="n">
         <v>0.5479849571775317</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.251215677415149</v>
+        <v>3.252842796031062</v>
       </c>
       <c r="F54" t="n">
-        <v>3.464607051783057</v>
+        <v>3.466039526347217</v>
       </c>
       <c r="G54" t="n">
-        <v>3.158346135933205</v>
+        <v>3.15969262107788</v>
       </c>
       <c r="H54" t="n">
-        <v>2.636343591877181</v>
+        <v>2.637507703834395</v>
       </c>
       <c r="I54" t="n">
-        <v>2.041922187438677</v>
+        <v>2.042827397375737</v>
       </c>
       <c r="J54" t="n">
-        <v>1.622891693565022</v>
+        <v>1.62359342681366</v>
       </c>
       <c r="K54" t="n">
-        <v>1.29934139731922</v>
+        <v>1.299879404365599</v>
       </c>
       <c r="L54" t="n">
-        <v>1.085953183242614</v>
+        <v>1.086377627325891</v>
       </c>
       <c r="M54" t="n">
-        <v>0.9591406671532405</v>
+        <v>0.9594918664098193</v>
       </c>
       <c r="N54" t="n">
-        <v>0.8671798032808025</v>
+        <v>0.8674762466001562</v>
       </c>
       <c r="O54" t="n">
-        <v>0.7486670104221232</v>
+        <v>0.7489066474644033</v>
       </c>
       <c r="P54" t="n">
-        <v>0.5340787477038575</v>
+        <v>0.5342383444461952</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.2595104631424987</v>
+        <v>0.2595823062523902</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.03549441683228143</v>
+        <v>-0.03550339052405017</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.3304926887598871</v>
+        <v>-0.330567868119647</v>
       </c>
       <c r="T54" t="n">
-        <v>-0.6034876687674701</v>
+        <v>-0.6036085583566269</v>
       </c>
       <c r="U54" t="n">
-        <v>-0.8591234252852453</v>
+        <v>-0.859271646948243</v>
       </c>
       <c r="V54" t="n">
-        <v>-1.075581612849415</v>
+        <v>-1.075735965647468</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>9.541030107695253</v>
+        <v>9.532509090592759</v>
       </c>
       <c r="F55" t="n">
-        <v>11.52841536626865</v>
+        <v>11.52073626177088</v>
       </c>
       <c r="G55" t="n">
-        <v>11.48190343665409</v>
+        <v>11.47451699050411</v>
       </c>
       <c r="H55" t="n">
-        <v>10.14636951234625</v>
+        <v>10.13984086965951</v>
       </c>
       <c r="I55" t="n">
-        <v>8.116893067053608</v>
+        <v>8.111707602575228</v>
       </c>
       <c r="J55" t="n">
-        <v>6.531947576746764</v>
+        <v>6.5278417566097</v>
       </c>
       <c r="K55" t="n">
-        <v>5.218739936405335</v>
+        <v>5.215525207219387</v>
       </c>
       <c r="L55" t="n">
-        <v>4.307981348579481</v>
+        <v>4.30539141057902</v>
       </c>
       <c r="M55" t="n">
-        <v>3.736953312157294</v>
+        <v>3.73476549606942</v>
       </c>
       <c r="N55" t="n">
-        <v>3.306811609371269</v>
+        <v>3.304928933256687</v>
       </c>
       <c r="O55" t="n">
-        <v>2.79315210898833</v>
+        <v>2.7916052767436</v>
       </c>
       <c r="P55" t="n">
-        <v>1.946838269430196</v>
+        <v>1.945794543581245</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.9222275685803397</v>
+        <v>0.921752956177514</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.1226025868562636</v>
+        <v>-0.1225428549559236</v>
       </c>
       <c r="S55" t="n">
-        <v>-1.106381340328608</v>
+        <v>-1.105878183504211</v>
       </c>
       <c r="T55" t="n">
-        <v>-1.955486137867339</v>
+        <v>-1.954674817356102</v>
       </c>
       <c r="U55" t="n">
-        <v>-2.700899688658366</v>
+        <v>-2.699906121244967</v>
       </c>
       <c r="V55" t="n">
-        <v>-3.282979990147344</v>
+        <v>-3.281949149711131</v>
       </c>
     </row>
     <row r="56">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.0005132723445018102</v>
+        <v>0.0005160171163975417</v>
       </c>
       <c r="F58" t="n">
-        <v>0.000625167688208035</v>
+        <v>0.0006277725535755685</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0006786884346001353</v>
+        <v>0.0006811836126685182</v>
       </c>
       <c r="H58" t="n">
         <v>0.0006898930665746809</v>
@@ -4937,7 +4937,7 @@
         <v>0.001442477136555714</v>
       </c>
       <c r="F60" t="n">
-        <v>0.002770774478490326</v>
+        <v>0.002774391677548407</v>
       </c>
       <c r="G60" t="n">
         <v>0.004804787420719199</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.0077823281201269</v>
+        <v>0.007784132044022157</v>
       </c>
       <c r="F61" t="n">
-        <v>0.009861078200393319</v>
+        <v>0.009862210161387452</v>
       </c>
       <c r="G61" t="n">
-        <v>0.01285557177320538</v>
+        <v>0.01285610990340742</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01589330701763302</v>
+        <v>0.01589382386754308</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01739309709427829</v>
+        <v>0.0173934304262783</v>
       </c>
       <c r="J61" t="n">
         <v>0.016716645343117</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.004982834933527307</v>
+        <v>0.004985966428583571</v>
       </c>
       <c r="F62" t="n">
-        <v>0.004125463521230247</v>
+        <v>0.004127547271691163</v>
       </c>
       <c r="G62" t="n">
-        <v>0.003880463583192569</v>
+        <v>0.003882033611536199</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00386044869470803</v>
+        <v>0.003861492700501313</v>
       </c>
       <c r="I62" t="n">
-        <v>0.00367963603397252</v>
+        <v>0.00368012713666504</v>
       </c>
       <c r="J62" t="n">
         <v>0.003266638441009708</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.008990645604159546</v>
+        <v>0.008993414306745514</v>
       </c>
       <c r="F63" t="n">
-        <v>0.009721916949923892</v>
+        <v>0.009723467378526199</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01206411203772124</v>
+        <v>0.01206516766951687</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01437817671198469</v>
+        <v>0.01437886252600735</v>
       </c>
       <c r="I63" t="n">
-        <v>0.01486285594992373</v>
+        <v>0.01486319266499881</v>
       </c>
       <c r="J63" t="n">
         <v>0.01311761820654323</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.04803792594791676</v>
+        <v>0.04803903923405913</v>
       </c>
       <c r="F65" t="n">
-        <v>0.05619859785294856</v>
+        <v>0.05619920355580615</v>
       </c>
       <c r="G65" t="n">
-        <v>0.06502733668758058</v>
+        <v>0.06502778054503723</v>
       </c>
       <c r="H65" t="n">
-        <v>0.07175123569627057</v>
+        <v>0.07175150268142086</v>
       </c>
       <c r="I65" t="n">
-        <v>0.07046671246175069</v>
+        <v>0.07046683411339069</v>
       </c>
       <c r="J65" t="n">
         <v>0.06230275239262013</v>
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.2457830711331276</v>
+        <v>0.2457837888726215</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2897356343212897</v>
+        <v>0.2897359609352307</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3353452071122878</v>
+        <v>0.3353454067722668</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3690383012963955</v>
+        <v>0.3690383935731113</v>
       </c>
       <c r="I66" t="n">
         <v>0.3620385084286121</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.330806228060925</v>
+        <v>4.330791727556232</v>
       </c>
       <c r="F67" t="n">
-        <v>4.237998553935362</v>
+        <v>4.237990540030346</v>
       </c>
       <c r="G67" t="n">
-        <v>3.820549920904222</v>
+        <v>3.820545011803003</v>
       </c>
       <c r="H67" t="n">
-        <v>3.324336079013527</v>
+        <v>3.324333169826232</v>
       </c>
       <c r="I67" t="n">
-        <v>2.641520177915645</v>
+        <v>2.64151893461973</v>
       </c>
       <c r="J67" t="n">
         <v>1.923915948224034</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.01528271271662456</v>
+        <v>0.01528595431862426</v>
       </c>
       <c r="F68" t="n">
-        <v>0.01231495157352555</v>
+        <v>0.01231673753976007</v>
       </c>
       <c r="G68" t="n">
-        <v>0.008671281298023173</v>
+        <v>0.008673067791347584</v>
       </c>
       <c r="H68" t="n">
-        <v>0.006493274629485159</v>
+        <v>0.006494356661584723</v>
       </c>
       <c r="I68" t="n">
-        <v>0.005055110189239675</v>
+        <v>0.005055842866997374</v>
       </c>
       <c r="J68" t="n">
         <v>0.004005045053949058</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.217543213963855</v>
+        <v>1.217540092190885</v>
       </c>
       <c r="F70" t="n">
-        <v>1.361467056909131</v>
+        <v>1.361465004109547</v>
       </c>
       <c r="G70" t="n">
-        <v>1.460588255635689</v>
+        <v>1.46058671871698</v>
       </c>
       <c r="H70" t="n">
-        <v>1.501871953959695</v>
+        <v>1.501870894434511</v>
       </c>
       <c r="I70" t="n">
-        <v>1.382946956383769</v>
+        <v>1.382946505629025</v>
       </c>
       <c r="J70" t="n">
         <v>1.13826034176636</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.006790336556644296</v>
+        <v>0.006793794093569461</v>
       </c>
       <c r="F71" t="n">
-        <v>0.006035481406151777</v>
+        <v>0.006037488216261885</v>
       </c>
       <c r="G71" t="n">
-        <v>0.006764289250709825</v>
+        <v>0.006765721553628524</v>
       </c>
       <c r="H71" t="n">
-        <v>0.008026818011295778</v>
+        <v>0.008027735807712471</v>
       </c>
       <c r="I71" t="n">
-        <v>0.008824295701382009</v>
+        <v>0.008824740306279421</v>
       </c>
       <c r="J71" t="n">
         <v>0.008526765492342697</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.04972015979950226</v>
+        <v>0.04972143360980325</v>
       </c>
       <c r="F72" t="n">
-        <v>0.06398953485797082</v>
+        <v>0.06399016757514307</v>
       </c>
       <c r="G72" t="n">
-        <v>0.07746079556753731</v>
+        <v>0.07746127246359256</v>
       </c>
       <c r="H72" t="n">
-        <v>0.08610409772017655</v>
+        <v>0.08610425902996038</v>
       </c>
       <c r="I72" t="n">
-        <v>0.08207607003042834</v>
+        <v>0.08207623455241382</v>
       </c>
       <c r="J72" t="n">
         <v>0.06809960792882028</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.0003876931740204298</v>
+        <v>0.0004201237817331653</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0007955151180957633</v>
+        <v>0.0008109548754710045</v>
       </c>
       <c r="G73" t="n">
-        <v>0.002176437307645597</v>
+        <v>0.002183842674463037</v>
       </c>
       <c r="H73" t="n">
-        <v>0.004721886527234939</v>
+        <v>0.004725648986619189</v>
       </c>
       <c r="I73" t="n">
-        <v>0.006623331666602562</v>
+        <v>0.006625639447671065</v>
       </c>
       <c r="J73" t="n">
         <v>0.006539482780602649</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.7170974685269361</v>
+        <v>0.6656037083671044</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8188227888571608</v>
+        <v>0.7475065993238494</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8553234375990204</v>
+        <v>0.777836607947797</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7938543130092722</v>
+        <v>0.7098651306546783</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7741272459114059</v>
+        <v>0.6722996389104832</v>
       </c>
       <c r="J75" t="n">
         <v>1.08898669860844</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9212095578009369</v>
+        <v>1.007060456876474</v>
       </c>
       <c r="F76" t="n">
-        <v>1.041954304129321</v>
+        <v>1.114036814666765</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9367844762150698</v>
+        <v>0.9578554045277053</v>
       </c>
       <c r="H76" t="n">
-        <v>0.7539475454975859</v>
+        <v>0.734171622983627</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6709266141902154</v>
+        <v>0.6164434988880938</v>
       </c>
       <c r="J76" t="n">
         <v>0.8672661246487099</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8661892850542893</v>
+        <v>0.8410052403706538</v>
       </c>
       <c r="F77" t="n">
-        <v>1.039139328352269</v>
+        <v>1.029616839584567</v>
       </c>
       <c r="G77" t="n">
-        <v>1.131479057608285</v>
+        <v>1.129167047503775</v>
       </c>
       <c r="H77" t="n">
-        <v>1.000856670172116</v>
+        <v>0.9903981996057503</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8559708412755653</v>
+        <v>0.8229690471337409</v>
       </c>
       <c r="J77" t="n">
         <v>0.9716486107279275</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2.936761843172043</v>
+        <v>3.317565843126703</v>
       </c>
       <c r="F78" t="n">
-        <v>2.856081920188009</v>
+        <v>3.129442422008202</v>
       </c>
       <c r="G78" t="n">
-        <v>2.561361349821251</v>
+        <v>2.727382547769053</v>
       </c>
       <c r="H78" t="n">
-        <v>1.986318636450765</v>
+        <v>2.089961297556749</v>
       </c>
       <c r="I78" t="n">
-        <v>1.496259100891131</v>
+        <v>1.573923125139719</v>
       </c>
       <c r="J78" t="n">
         <v>1.071270432696885</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1.261638153506988</v>
+        <v>1.000542346956636</v>
       </c>
       <c r="F79" t="n">
-        <v>1.316843080536767</v>
+        <v>1.11212405663455</v>
       </c>
       <c r="G79" t="n">
-        <v>1.349607098198118</v>
+        <v>1.226589202375177</v>
       </c>
       <c r="H79" t="n">
-        <v>1.268863018986775</v>
+        <v>1.1964374474195</v>
       </c>
       <c r="I79" t="n">
-        <v>1.142362410892602</v>
+        <v>1.093645307870319</v>
       </c>
       <c r="J79" t="n">
         <v>1.118738492683975</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2.211436281706396</v>
+        <v>2.111250434915436</v>
       </c>
       <c r="F80" t="n">
-        <v>2.511744155419389</v>
+        <v>2.185387044975283</v>
       </c>
       <c r="G80" t="n">
-        <v>2.727248973000652</v>
+        <v>2.195937760542359</v>
       </c>
       <c r="H80" t="n">
-        <v>2.821027665165437</v>
+        <v>2.143384317109904</v>
       </c>
       <c r="I80" t="n">
-        <v>3.333414803494565</v>
+        <v>2.479075730425036</v>
       </c>
       <c r="J80" t="n">
         <v>6.291148527167774</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.128376456091416</v>
+        <v>0.7760090499445675</v>
       </c>
       <c r="F81" t="n">
-        <v>1.032614474159267</v>
+        <v>0.7424467461658809</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9126340680157621</v>
+        <v>0.7032478248068696</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8273276744723718</v>
+        <v>0.6630026068305083</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8335815758432181</v>
+        <v>0.6767188169464541</v>
       </c>
       <c r="J81" t="n">
         <v>1.247078887117932</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.078029952214116</v>
+        <v>3.418536611334616</v>
       </c>
       <c r="F82" t="n">
-        <v>3.404944131079426</v>
+        <v>3.691844675406069</v>
       </c>
       <c r="G82" t="n">
-        <v>3.414196523879956</v>
+        <v>3.632713722811866</v>
       </c>
       <c r="H82" t="n">
-        <v>2.849022621936864</v>
+        <v>3.037809137509963</v>
       </c>
       <c r="I82" t="n">
-        <v>2.146599461200515</v>
+        <v>2.349676917703056</v>
       </c>
       <c r="J82" t="n">
         <v>1.092552096545419</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.591704051582644</v>
+        <v>1.436798852014986</v>
       </c>
       <c r="F83" t="n">
-        <v>1.862837751476265</v>
+        <v>1.782567597385037</v>
       </c>
       <c r="G83" t="n">
-        <v>2.126776281033225</v>
+        <v>2.124780087777737</v>
       </c>
       <c r="H83" t="n">
-        <v>2.021575832841551</v>
+        <v>2.072022003748355</v>
       </c>
       <c r="I83" t="n">
-        <v>1.676036782621241</v>
+        <v>1.768553253692092</v>
       </c>
       <c r="J83" t="n">
         <v>1.064139764640144</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.852597592891097</v>
+        <v>2.826969577423009</v>
       </c>
       <c r="F86" t="n">
-        <v>3.280487742468883</v>
+        <v>3.259071215563497</v>
       </c>
       <c r="G86" t="n">
-        <v>3.446219291457046</v>
+        <v>3.428166771843268</v>
       </c>
       <c r="H86" t="n">
-        <v>3.158921179076729</v>
+        <v>3.147424961038578</v>
       </c>
       <c r="I86" t="n">
-        <v>2.58906006593893</v>
+        <v>2.584235983873473</v>
       </c>
       <c r="J86" t="n">
         <v>2.175142770050808</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.115605054834559</v>
+        <v>1.128150111202952</v>
       </c>
       <c r="F87" t="n">
-        <v>1.1951812032545</v>
+        <v>1.206159207698324</v>
       </c>
       <c r="G87" t="n">
-        <v>1.104187785586857</v>
+        <v>1.114542090457278</v>
       </c>
       <c r="H87" t="n">
-        <v>0.910656074591632</v>
+        <v>0.917413122085337</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6921131686384704</v>
+        <v>0.6948497742983404</v>
       </c>
       <c r="J87" t="n">
         <v>0.5522589100440497</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9507957714133455</v>
+        <v>0.9980519135686875</v>
       </c>
       <c r="F88" t="n">
-        <v>1.382403503929173</v>
+        <v>1.404644760384178</v>
       </c>
       <c r="G88" t="n">
-        <v>1.742454467513734</v>
+        <v>1.750411119225937</v>
       </c>
       <c r="H88" t="n">
-        <v>1.726080475285429</v>
+        <v>1.727949202966922</v>
       </c>
       <c r="I88" t="n">
-        <v>1.423083446710382</v>
+        <v>1.4234048119986</v>
       </c>
       <c r="J88" t="n">
         <v>1.15422054886272</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.595330172456518</v>
+        <v>1.660914111157334</v>
       </c>
       <c r="F89" t="n">
-        <v>1.98116991347333</v>
+        <v>2.021902371795115</v>
       </c>
       <c r="G89" t="n">
-        <v>2.056886421366741</v>
+        <v>2.084857980468076</v>
       </c>
       <c r="H89" t="n">
-        <v>1.830680636082074</v>
+        <v>1.845966390183201</v>
       </c>
       <c r="I89" t="n">
-        <v>1.451081862646309</v>
+        <v>1.456752684663589</v>
       </c>
       <c r="J89" t="n">
         <v>1.180431982094816</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.561963141522682</v>
+        <v>1.555593903901125</v>
       </c>
       <c r="F90" t="n">
-        <v>1.92589095802629</v>
+        <v>1.916643656235937</v>
       </c>
       <c r="G90" t="n">
-        <v>1.931617964870188</v>
+        <v>1.92500019952006</v>
       </c>
       <c r="H90" t="n">
-        <v>1.633730634743152</v>
+        <v>1.630754891246479</v>
       </c>
       <c r="I90" t="n">
-        <v>1.2341479281743</v>
+        <v>1.233323896321372</v>
       </c>
       <c r="J90" t="n">
         <v>0.9653969710361784</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.739171053401632</v>
+        <v>1.723668655456749</v>
       </c>
       <c r="F91" t="n">
-        <v>2.019557537941876</v>
+        <v>2.006135691985673</v>
       </c>
       <c r="G91" t="n">
-        <v>2.07783399094515</v>
+        <v>2.067282226820563</v>
       </c>
       <c r="H91" t="n">
-        <v>1.905514893856863</v>
+        <v>1.89875706715085</v>
       </c>
       <c r="I91" t="n">
-        <v>1.591736678831545</v>
+        <v>1.588743095244975</v>
       </c>
       <c r="J91" t="n">
         <v>1.375457619357779</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.182763011482913</v>
+        <v>2.150631502873596</v>
       </c>
       <c r="F92" t="n">
-        <v>2.467617626479297</v>
+        <v>2.442859564024803</v>
       </c>
       <c r="G92" t="n">
-        <v>2.370566415814938</v>
+        <v>2.354262925097493</v>
       </c>
       <c r="H92" t="n">
-        <v>2.05854222285025</v>
+        <v>2.049649509717337</v>
       </c>
       <c r="I92" t="n">
-        <v>1.652240638588651</v>
+        <v>1.648747541551626</v>
       </c>
       <c r="J92" t="n">
         <v>1.386168088817269</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9107977123990332</v>
+        <v>0.9151300041271152</v>
       </c>
       <c r="F93" t="n">
-        <v>1.01501963981668</v>
+        <v>1.018339012736264</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9296728084611756</v>
+        <v>0.9340622158796654</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7207887569952772</v>
+        <v>0.7246566999528861</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5058253637677612</v>
+        <v>0.507746371558002</v>
       </c>
       <c r="J93" t="n">
         <v>0.3753081409857247</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1.315263201700956</v>
+        <v>1.337857039050333</v>
       </c>
       <c r="F94" t="n">
-        <v>1.37663765019412</v>
+        <v>1.396640679319237</v>
       </c>
       <c r="G94" t="n">
-        <v>1.337300353218945</v>
+        <v>1.353115519819537</v>
       </c>
       <c r="H94" t="n">
-        <v>1.153251403563061</v>
+        <v>1.162479407040655</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9024643564722457</v>
+        <v>0.9059781997023373</v>
       </c>
       <c r="J94" t="n">
         <v>0.727585411083841</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3.318722793179842</v>
+        <v>3.258918957077422</v>
       </c>
       <c r="F95" t="n">
-        <v>3.381417875352287</v>
+        <v>3.343214661502777</v>
       </c>
       <c r="G95" t="n">
-        <v>3.105589380162833</v>
+        <v>3.082244904023296</v>
       </c>
       <c r="H95" t="n">
-        <v>2.575492335557732</v>
+        <v>2.563934260806104</v>
       </c>
       <c r="I95" t="n">
-        <v>1.96231865914547</v>
+        <v>1.958294338693694</v>
       </c>
       <c r="J95" t="n">
         <v>1.57329184661829</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.03182097752882</v>
+        <v>1.049450602145405</v>
       </c>
       <c r="F96" t="n">
-        <v>1.389500847029959</v>
+        <v>1.395361795620991</v>
       </c>
       <c r="G96" t="n">
-        <v>1.71412099046431</v>
+        <v>1.712159632506468</v>
       </c>
       <c r="H96" t="n">
-        <v>1.702141206695503</v>
+        <v>1.698769688431646</v>
       </c>
       <c r="I96" t="n">
-        <v>1.418134114634791</v>
+        <v>1.416454717738412</v>
       </c>
       <c r="J96" t="n">
         <v>1.161229210143988</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8445518691790598</v>
+        <v>0.8720561382123487</v>
       </c>
       <c r="F97" t="n">
-        <v>1.309352694248894</v>
+        <v>1.317452303104081</v>
       </c>
       <c r="G97" t="n">
-        <v>1.714749542605208</v>
+        <v>1.712692998144619</v>
       </c>
       <c r="H97" t="n">
-        <v>1.735853945425178</v>
+        <v>1.73205751900957</v>
       </c>
       <c r="I97" t="n">
-        <v>1.446778273028356</v>
+        <v>1.444931423172</v>
       </c>
       <c r="J97" t="n">
         <v>1.182125362725547</v>
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1.210538942469664</v>
+        <v>1.210650110277528</v>
       </c>
       <c r="F98" t="n">
-        <v>1.568870236937111</v>
+        <v>1.568916738288773</v>
       </c>
       <c r="G98" t="n">
-        <v>1.902763136180351</v>
+        <v>1.902761761890272</v>
       </c>
       <c r="H98" t="n">
-        <v>2.047018624616717</v>
+        <v>2.046980486946329</v>
       </c>
       <c r="I98" t="n">
-        <v>1.839255829496037</v>
+        <v>1.839200438046479</v>
       </c>
       <c r="J98" t="n">
-        <v>1.551514198186383</v>
+        <v>1.5514555230705</v>
       </c>
       <c r="K98" t="n">
-        <v>1.21859943234315</v>
+        <v>1.218546407950109</v>
       </c>
       <c r="L98" t="n">
-        <v>0.9711023934835886</v>
+        <v>0.9710557737253334</v>
       </c>
       <c r="M98" t="n">
-        <v>0.7897395054383985</v>
+        <v>0.7896987336658086</v>
       </c>
       <c r="N98" t="n">
-        <v>0.6562974301518777</v>
+        <v>0.6562614329384855</v>
       </c>
       <c r="O98" t="n">
-        <v>0.5409269501340993</v>
+        <v>0.5408957139651145</v>
       </c>
       <c r="P98" t="n">
-        <v>0.481104185617465</v>
+        <v>0.4810751126699905</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.423491606627073</v>
+        <v>0.4234652378866063</v>
       </c>
       <c r="R98" t="n">
-        <v>0.4033153731189986</v>
+        <v>0.4032898267141506</v>
       </c>
       <c r="S98" t="n">
-        <v>0.3534988258398722</v>
+        <v>0.3534763883598705</v>
       </c>
       <c r="T98" t="n">
-        <v>0.2273090507773211</v>
+        <v>0.2272947327309831</v>
       </c>
       <c r="U98" t="n">
-        <v>0.09064360446421742</v>
+        <v>0.09063796070009408</v>
       </c>
       <c r="V98" t="n">
-        <v>-0.04343444243551148</v>
+        <v>-0.04343193735803257</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1.195039412202699</v>
+        <v>1.195196076733722</v>
       </c>
       <c r="F99" t="n">
-        <v>1.038634946228381</v>
+        <v>1.03878088434382</v>
       </c>
       <c r="G99" t="n">
-        <v>0.8151532273063427</v>
+        <v>0.8153150619969659</v>
       </c>
       <c r="H99" t="n">
-        <v>0.6321138037764333</v>
+        <v>0.6322813314703649</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4566872499963291</v>
+        <v>0.4568341750645443</v>
       </c>
       <c r="J99" t="n">
-        <v>0.3381200408104776</v>
+        <v>0.3382428326384283</v>
       </c>
       <c r="K99" t="n">
-        <v>0.2469375008021494</v>
+        <v>0.2470341865350144</v>
       </c>
       <c r="L99" t="n">
-        <v>0.1900392937745158</v>
+        <v>0.190117521459062</v>
       </c>
       <c r="M99" t="n">
-        <v>0.1524871390515497</v>
+        <v>0.1525523373638006</v>
       </c>
       <c r="N99" t="n">
-        <v>0.1262683489684799</v>
+        <v>0.1263240223075513</v>
       </c>
       <c r="O99" t="n">
-        <v>0.104104621998023</v>
+        <v>0.1041518480604775</v>
       </c>
       <c r="P99" t="n">
-        <v>0.09269213107313945</v>
+        <v>0.09273510382251987</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.08175794976583921</v>
+        <v>0.08179619496674945</v>
       </c>
       <c r="R99" t="n">
-        <v>0.07823664176900423</v>
+        <v>0.07827325689188849</v>
       </c>
       <c r="S99" t="n">
-        <v>0.06898762104489368</v>
+        <v>0.06901939876928319</v>
       </c>
       <c r="T99" t="n">
-        <v>0.04451568182334337</v>
+        <v>0.0445355291078695</v>
       </c>
       <c r="U99" t="n">
-        <v>0.01777554826450603</v>
+        <v>0.01778301711123016</v>
       </c>
       <c r="V99" t="n">
-        <v>-0.008508013796248302</v>
+        <v>-0.008511322812228073</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.734585094249365</v>
+        <v>1.734583504988249</v>
       </c>
       <c r="F100" t="n">
-        <v>2.325144540278071</v>
+        <v>2.325093331028049</v>
       </c>
       <c r="G100" t="n">
-        <v>2.762966209381296</v>
+        <v>2.762866727677554</v>
       </c>
       <c r="H100" t="n">
-        <v>2.908251685400851</v>
+        <v>2.908117545992162</v>
       </c>
       <c r="I100" t="n">
-        <v>2.577010662548618</v>
+        <v>2.576872207459632</v>
       </c>
       <c r="J100" t="n">
-        <v>2.16603908959338</v>
+        <v>2.165909636222717</v>
       </c>
       <c r="K100" t="n">
-        <v>1.703772876311437</v>
+        <v>1.70366244823684</v>
       </c>
       <c r="L100" t="n">
-        <v>1.366721883650085</v>
+        <v>1.366626800004638</v>
       </c>
       <c r="M100" t="n">
-        <v>1.121556762012749</v>
+        <v>1.121473687038165</v>
       </c>
       <c r="N100" t="n">
-        <v>0.9408527401806327</v>
+        <v>0.9407790485562929</v>
       </c>
       <c r="O100" t="n">
-        <v>0.7827235196350575</v>
+        <v>0.782659073519292</v>
       </c>
       <c r="P100" t="n">
-        <v>0.7010708830988798</v>
+        <v>0.7010107429554522</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.6202601868435197</v>
+        <v>0.6202054632294081</v>
       </c>
       <c r="R100" t="n">
-        <v>0.5936626020807696</v>
+        <v>0.5936092730647126</v>
       </c>
       <c r="S100" t="n">
-        <v>0.5222575726473081</v>
+        <v>0.522210459738743</v>
       </c>
       <c r="T100" t="n">
-        <v>0.335807455684865</v>
+        <v>0.3357777270618749</v>
       </c>
       <c r="U100" t="n">
-        <v>0.1339600253437332</v>
+        <v>0.1339484817685055</v>
       </c>
       <c r="V100" t="n">
-        <v>-0.0645228693459816</v>
+        <v>-0.06451768877427673</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1.676332200690175</v>
+        <v>1.676409247933098</v>
       </c>
       <c r="F101" t="n">
-        <v>1.843889333239517</v>
+        <v>1.843936002021835</v>
       </c>
       <c r="G101" t="n">
-        <v>1.827192704417982</v>
+        <v>1.827226190220976</v>
       </c>
       <c r="H101" t="n">
-        <v>1.684425612503183</v>
+        <v>1.684449707413916</v>
       </c>
       <c r="I101" t="n">
-        <v>1.371330229607373</v>
+        <v>1.371344425079017</v>
       </c>
       <c r="J101" t="n">
-        <v>1.096492698588871</v>
+        <v>1.096499530277607</v>
       </c>
       <c r="K101" t="n">
-        <v>0.8400514263692465</v>
+        <v>0.840053532281173</v>
       </c>
       <c r="L101" t="n">
-        <v>0.6657813702373779</v>
+        <v>0.6657806657107413</v>
       </c>
       <c r="M101" t="n">
-        <v>0.5442541662316243</v>
+        <v>0.5442516887019337</v>
       </c>
       <c r="N101" t="n">
-        <v>0.4556528446098465</v>
+        <v>0.4556494617093048</v>
       </c>
       <c r="O101" t="n">
-        <v>0.3778799981541437</v>
+        <v>0.3778764069940715</v>
       </c>
       <c r="P101" t="n">
-        <v>0.3367572150032858</v>
+        <v>0.3367535843562682</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.2962271770477247</v>
+        <v>0.2962236798414403</v>
       </c>
       <c r="R101" t="n">
-        <v>0.2820690295942272</v>
+        <v>0.2820652831575567</v>
       </c>
       <c r="S101" t="n">
-        <v>0.2478366565696609</v>
+        <v>0.2478332126692677</v>
       </c>
       <c r="T101" t="n">
-        <v>0.1597089330965361</v>
+        <v>0.1597065800266328</v>
       </c>
       <c r="U101" t="n">
-        <v>0.06375830735755479</v>
+        <v>0.06375729878529575</v>
       </c>
       <c r="V101" t="n">
-        <v>-0.03056834689043321</v>
+        <v>-0.03056792970611033</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1.804867980943166</v>
+        <v>1.804832759952758</v>
       </c>
       <c r="F102" t="n">
-        <v>1.729985388085053</v>
+        <v>1.729974714508278</v>
       </c>
       <c r="G102" t="n">
-        <v>1.452823658339457</v>
+        <v>1.452831486092199</v>
       </c>
       <c r="H102" t="n">
-        <v>1.158106241455792</v>
+        <v>1.15812777554989</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8382838168062211</v>
+        <v>0.8383100316066594</v>
       </c>
       <c r="J102" t="n">
-        <v>0.6144495166726823</v>
+        <v>0.6144750781016171</v>
       </c>
       <c r="K102" t="n">
-        <v>0.4427708441004028</v>
+        <v>0.4427925990125344</v>
       </c>
       <c r="L102" t="n">
-        <v>0.3365852715607195</v>
+        <v>0.3366035129893067</v>
       </c>
       <c r="M102" t="n">
-        <v>0.2679443579102158</v>
+        <v>0.2679596622725863</v>
       </c>
       <c r="N102" t="n">
-        <v>0.2210870923170105</v>
+        <v>0.2211000682422045</v>
       </c>
       <c r="O102" t="n">
-        <v>0.1822301251474388</v>
+        <v>0.1822409358114026</v>
       </c>
       <c r="P102" t="n">
-        <v>0.162238856151102</v>
+        <v>0.1622485326449266</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.1429426157534399</v>
+        <v>0.1429511082657566</v>
       </c>
       <c r="R102" t="n">
-        <v>0.136447338108252</v>
+        <v>0.1364553524801178</v>
       </c>
       <c r="S102" t="n">
-        <v>0.1197749582085858</v>
+        <v>0.1197818669644719</v>
       </c>
       <c r="T102" t="n">
-        <v>0.07663400369611212</v>
+        <v>0.07663833159176434</v>
       </c>
       <c r="U102" t="n">
-        <v>0.03036101924550733</v>
+        <v>0.03036266573731351</v>
       </c>
       <c r="V102" t="n">
-        <v>-0.01448551801224733</v>
+        <v>-0.01448622406416349</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1.92759590422766</v>
+        <v>1.927682198694688</v>
       </c>
       <c r="F103" t="n">
-        <v>2.633646677968868</v>
+        <v>2.633644493612906</v>
       </c>
       <c r="G103" t="n">
-        <v>3.286949751561254</v>
+        <v>3.286870416413049</v>
       </c>
       <c r="H103" t="n">
-        <v>3.577056807229533</v>
+        <v>3.576920516805483</v>
       </c>
       <c r="I103" t="n">
-        <v>3.207182772393556</v>
+        <v>3.207031556132639</v>
       </c>
       <c r="J103" t="n">
-        <v>2.683929136666506</v>
+        <v>2.683785963872011</v>
       </c>
       <c r="K103" t="n">
-        <v>2.076810859288071</v>
+        <v>2.076690457827763</v>
       </c>
       <c r="L103" t="n">
-        <v>1.62662782228307</v>
+        <v>1.626527580149278</v>
       </c>
       <c r="M103" t="n">
-        <v>1.29979735733255</v>
+        <v>1.299713106626992</v>
       </c>
       <c r="N103" t="n">
-        <v>1.064607166901632</v>
+        <v>1.06453505955819</v>
       </c>
       <c r="O103" t="n">
-        <v>0.867044857706388</v>
+        <v>0.8669837585090809</v>
       </c>
       <c r="P103" t="n">
-        <v>0.7624473676147832</v>
+        <v>0.7623919497652437</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.662724717048721</v>
+        <v>0.6626756256641355</v>
       </c>
       <c r="R103" t="n">
-        <v>0.6220884824446788</v>
+        <v>0.6220421472495024</v>
       </c>
       <c r="S103" t="n">
-        <v>0.5373297320220319</v>
+        <v>0.5372900915930617</v>
       </c>
       <c r="T103" t="n">
-        <v>0.340602211621169</v>
+        <v>0.3405777003366646</v>
       </c>
       <c r="U103" t="n">
-        <v>0.1343507736565452</v>
+        <v>0.1343415467441582</v>
       </c>
       <c r="V103" t="n">
-        <v>-0.06349055608314867</v>
+        <v>-0.06348653907177822</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2.392255843931946</v>
+        <v>2.392186008168509</v>
       </c>
       <c r="F104" t="n">
-        <v>2.361442803130221</v>
+        <v>2.361404378791876</v>
       </c>
       <c r="G104" t="n">
-        <v>2.092180053660135</v>
+        <v>2.092156942611991</v>
       </c>
       <c r="H104" t="n">
-        <v>1.687038875960201</v>
+        <v>1.687034768149824</v>
       </c>
       <c r="I104" t="n">
-        <v>1.205338002367524</v>
+        <v>1.205347724520981</v>
       </c>
       <c r="J104" t="n">
-        <v>0.8628403116039501</v>
+        <v>0.8628565693593082</v>
       </c>
       <c r="K104" t="n">
-        <v>0.6088231240133277</v>
+        <v>0.6088399399404918</v>
       </c>
       <c r="L104" t="n">
-        <v>0.4576104558316756</v>
+        <v>0.4576255848485697</v>
       </c>
       <c r="M104" t="n">
-        <v>0.3622737515585263</v>
+        <v>0.362286810769178</v>
       </c>
       <c r="N104" t="n">
-        <v>0.2980401863829521</v>
+        <v>0.2980513178040245</v>
       </c>
       <c r="O104" t="n">
-        <v>0.2447699390186733</v>
+        <v>0.244779184247256</v>
       </c>
       <c r="P104" t="n">
-        <v>0.217518226659476</v>
+        <v>0.2175265299039273</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.1921848622224726</v>
+        <v>0.1921919581161649</v>
       </c>
       <c r="R104" t="n">
-        <v>0.1849020862007571</v>
+        <v>0.1849084489512066</v>
       </c>
       <c r="S104" t="n">
-        <v>0.1642410978588511</v>
+        <v>0.1642462066416731</v>
       </c>
       <c r="T104" t="n">
-        <v>0.10651078717314</v>
+        <v>0.106513810687373</v>
       </c>
       <c r="U104" t="n">
-        <v>0.0425226864906758</v>
+        <v>0.04252382307258756</v>
       </c>
       <c r="V104" t="n">
-        <v>-0.02027760708303929</v>
+        <v>-0.02027800473255949</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1.503186868686869</v>
+        <v>1.503267887205387</v>
       </c>
       <c r="F105" t="n">
-        <v>1.652230904349861</v>
+        <v>1.652281789755926</v>
       </c>
       <c r="G105" t="n">
-        <v>1.547404970127284</v>
+        <v>1.547453074340251</v>
       </c>
       <c r="H105" t="n">
-        <v>1.363924057113358</v>
+        <v>1.363969853839562</v>
       </c>
       <c r="I105" t="n">
-        <v>1.081892136044037</v>
+        <v>1.081928458498524</v>
       </c>
       <c r="J105" t="n">
-        <v>0.8622732555868621</v>
+        <v>0.8622992954116071</v>
       </c>
       <c r="K105" t="n">
-        <v>0.6667561221990097</v>
+        <v>0.6667729811262589</v>
       </c>
       <c r="L105" t="n">
-        <v>0.5359871443849146</v>
+        <v>0.5359976340687336</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4433443659224063</v>
+        <v>0.4433507266929232</v>
       </c>
       <c r="N105" t="n">
-        <v>0.374683518583842</v>
+        <v>0.3746873491706446</v>
       </c>
       <c r="O105" t="n">
-        <v>0.3134251807738975</v>
+        <v>0.3134275151152773</v>
       </c>
       <c r="P105" t="n">
-        <v>0.2827499635981043</v>
+        <v>0.2827511378528048</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.2531222815877281</v>
+        <v>0.2531224510581991</v>
       </c>
       <c r="R105" t="n">
-        <v>0.2465302091024672</v>
+        <v>0.2465293499349696</v>
       </c>
       <c r="S105" t="n">
-        <v>0.2215399524609782</v>
+        <v>0.2215383792472837</v>
       </c>
       <c r="T105" t="n">
-        <v>0.1453987580108691</v>
+        <v>0.1453971523134265</v>
       </c>
       <c r="U105" t="n">
-        <v>0.05882284142028617</v>
+        <v>0.05882211042934022</v>
       </c>
       <c r="V105" t="n">
-        <v>-0.02852650359002285</v>
+        <v>-0.02852612751388097</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2.452651893923591</v>
+        <v>2.452566222791226</v>
       </c>
       <c r="F106" t="n">
-        <v>2.147850956581435</v>
+        <v>2.147827248029878</v>
       </c>
       <c r="G106" t="n">
-        <v>1.608478590749287</v>
+        <v>1.608498240199184</v>
       </c>
       <c r="H106" t="n">
-        <v>1.178148348973578</v>
+        <v>1.178194963914002</v>
       </c>
       <c r="I106" t="n">
-        <v>0.8042968141968811</v>
+        <v>0.8043509475228273</v>
       </c>
       <c r="J106" t="n">
-        <v>0.5678631085023339</v>
+        <v>0.5679147909898425</v>
       </c>
       <c r="K106" t="n">
-        <v>0.4002101500457899</v>
+        <v>0.4002537914291009</v>
       </c>
       <c r="L106" t="n">
-        <v>0.3009850963298468</v>
+        <v>0.3010216192521987</v>
       </c>
       <c r="M106" t="n">
-        <v>0.2372690436572835</v>
+        <v>0.2373000589185653</v>
       </c>
       <c r="N106" t="n">
-        <v>0.193691112104763</v>
+        <v>0.1937179656349604</v>
       </c>
       <c r="O106" t="n">
-        <v>0.1578779996548425</v>
+        <v>0.1579010101535658</v>
       </c>
       <c r="P106" t="n">
-        <v>0.1395534592264621</v>
+        <v>0.1395744918071201</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.1227692123927071</v>
+        <v>0.1227879102052192</v>
       </c>
       <c r="R106" t="n">
-        <v>0.1175470621975358</v>
+        <v>0.1175648365535988</v>
       </c>
       <c r="S106" t="n">
-        <v>0.1035845030862774</v>
+        <v>0.103599846275853</v>
       </c>
       <c r="T106" t="n">
-        <v>0.06627602392045813</v>
+        <v>0.0662856444532753</v>
       </c>
       <c r="U106" t="n">
-        <v>0.02605905766431308</v>
+        <v>0.02606274102874787</v>
       </c>
       <c r="V106" t="n">
-        <v>-0.01230939740760353</v>
+        <v>-0.01231103076366971</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.08208264085355797</v>
+        <v>0.08258648219065864</v>
       </c>
       <c r="F107" t="n">
-        <v>0.07449773614416749</v>
+        <v>0.07489130268829698</v>
       </c>
       <c r="G107" t="n">
-        <v>0.07098960427316064</v>
+        <v>0.07135495440302746</v>
       </c>
       <c r="H107" t="n">
-        <v>0.06520193304980729</v>
+        <v>0.06553709163869904</v>
       </c>
       <c r="I107" t="n">
-        <v>0.05267048578166738</v>
+        <v>0.05294464675578573</v>
       </c>
       <c r="J107" t="n">
-        <v>0.04144384109902439</v>
+        <v>0.04166466643715461</v>
       </c>
       <c r="K107" t="n">
-        <v>0.03117683968531837</v>
+        <v>0.03134820618817624</v>
       </c>
       <c r="L107" t="n">
-        <v>0.0243473338789747</v>
+        <v>0.02448501908469935</v>
       </c>
       <c r="M107" t="n">
-        <v>0.01975005426861413</v>
+        <v>0.01986417341148014</v>
       </c>
       <c r="N107" t="n">
-        <v>0.01658218550242517</v>
+        <v>0.01667931354754114</v>
       </c>
       <c r="O107" t="n">
-        <v>0.01389306412727005</v>
+        <v>0.01397570390526847</v>
       </c>
       <c r="P107" t="n">
-        <v>0.01259319643696559</v>
+        <v>0.01266817010692673</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.01132317248902576</v>
+        <v>0.01138867254023489</v>
       </c>
       <c r="R107" t="n">
-        <v>0.0110554331975059</v>
+        <v>0.01111904604730155</v>
       </c>
       <c r="S107" t="n">
-        <v>0.009959882790520938</v>
+        <v>0.01001468772150326</v>
       </c>
       <c r="T107" t="n">
-        <v>0.006576460053725998</v>
+        <v>0.006610038802109243</v>
       </c>
       <c r="U107" t="n">
-        <v>0.002690253995762051</v>
+        <v>0.002703034299779924</v>
       </c>
       <c r="V107" t="n">
-        <v>-0.001321194582307907</v>
+        <v>-0.001326489951375274</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.8140867524379484</v>
+        <v>0.814305175096148</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8556137067291714</v>
+        <v>0.8557745747986962</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8483610098322131</v>
+        <v>0.8485038562780437</v>
       </c>
       <c r="H108" t="n">
-        <v>0.7864844260758649</v>
+        <v>0.7866115228294115</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6409809515192177</v>
+        <v>0.6410819614477824</v>
       </c>
       <c r="J108" t="n">
-        <v>0.5104564288444736</v>
+        <v>0.5105357256625892</v>
       </c>
       <c r="K108" t="n">
-        <v>0.3888865614326679</v>
+        <v>0.3889465489214808</v>
       </c>
       <c r="L108" t="n">
-        <v>0.3060753615794182</v>
+        <v>0.3061226471411195</v>
       </c>
       <c r="M108" t="n">
-        <v>0.2485373870934466</v>
+        <v>0.2485760416147506</v>
       </c>
       <c r="N108" t="n">
-        <v>0.2072369017901302</v>
+        <v>0.2072695028196672</v>
       </c>
       <c r="O108" t="n">
-        <v>0.1717687916574407</v>
+        <v>0.1717961439226464</v>
       </c>
       <c r="P108" t="n">
-        <v>0.1533277529505375</v>
+        <v>0.15335239697628</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.1351692608790582</v>
+        <v>0.1351911555329311</v>
       </c>
       <c r="R108" t="n">
-        <v>0.1287173036642901</v>
+        <v>0.1287382060667677</v>
       </c>
       <c r="S108" t="n">
-        <v>0.1124660651750482</v>
+        <v>0.1124843571810631</v>
       </c>
       <c r="T108" t="n">
-        <v>0.07179827137702442</v>
+        <v>0.07180982565307478</v>
       </c>
       <c r="U108" t="n">
-        <v>0.02845745068546704</v>
+        <v>0.02846182389228659</v>
       </c>
       <c r="V108" t="n">
-        <v>-0.01357239236154566</v>
+        <v>-0.01357430724104845</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6.482609671620526</v>
+        <v>6.482065649922734</v>
       </c>
       <c r="F109" t="n">
-        <v>6.599325151847746</v>
+        <v>6.598936720199275</v>
       </c>
       <c r="G109" t="n">
-        <v>5.2870582627965</v>
+        <v>5.286771921672202</v>
       </c>
       <c r="H109" t="n">
-        <v>3.706768195251889</v>
+        <v>3.706587311342302</v>
       </c>
       <c r="I109" t="n">
-        <v>2.27286883885854</v>
+        <v>2.272779642278629</v>
       </c>
       <c r="J109" t="n">
-        <v>1.435318826746939</v>
+        <v>1.435280005873607</v>
       </c>
       <c r="K109" t="n">
-        <v>0.9232203686635945</v>
+        <v>0.9232064516129033</v>
       </c>
       <c r="L109" t="n">
-        <v>0.6497487838760785</v>
+        <v>0.6497451598964843</v>
       </c>
       <c r="M109" t="n">
-        <v>0.491585331675598</v>
+        <v>0.4915858019106591</v>
       </c>
       <c r="N109" t="n">
-        <v>0.392253030926575</v>
+        <v>0.3922550361075808</v>
       </c>
       <c r="O109" t="n">
-        <v>0.315702616956758</v>
+        <v>0.315705148804481</v>
       </c>
       <c r="P109" t="n">
-        <v>0.276604439481778</v>
+        <v>0.2766071312852365</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.2415655758107157</v>
+        <v>0.2415680341545909</v>
       </c>
       <c r="R109" t="n">
-        <v>0.2302234028676852</v>
+        <v>0.2302256190403423</v>
       </c>
       <c r="S109" t="n">
-        <v>0.2028404705886454</v>
+        <v>0.2028421047585721</v>
       </c>
       <c r="T109" t="n">
-        <v>0.13065630872093</v>
+        <v>0.1306572101696031</v>
       </c>
       <c r="U109" t="n">
-        <v>0.05195242883670595</v>
+        <v>0.05195266247305005</v>
       </c>
       <c r="V109" t="n">
-        <v>-0.02475459711807722</v>
+        <v>-0.0247547187808225</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1.18462946508273</v>
+        <v>1.18463716040541</v>
       </c>
       <c r="F110" t="n">
-        <v>1.101526961828431</v>
+        <v>1.101547172054409</v>
       </c>
       <c r="G110" t="n">
-        <v>0.904510158728635</v>
+        <v>0.9045436611741215</v>
       </c>
       <c r="H110" t="n">
-        <v>0.7250563883716312</v>
+        <v>0.7250969467851135</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5410579620119482</v>
+        <v>0.541095122441321</v>
       </c>
       <c r="J110" t="n">
-        <v>0.4124784190599982</v>
+        <v>0.4125093839958089</v>
       </c>
       <c r="K110" t="n">
-        <v>0.3092775549782509</v>
+        <v>0.3093011559155705</v>
       </c>
       <c r="L110" t="n">
-        <v>0.2432324467525329</v>
+        <v>0.2432507982010362</v>
       </c>
       <c r="M110" t="n">
-        <v>0.198410271196098</v>
+        <v>0.1984248590130398</v>
       </c>
       <c r="N110" t="n">
-        <v>0.1660246460475845</v>
+        <v>0.1660366249952212</v>
       </c>
       <c r="O110" t="n">
-        <v>0.1376144081804861</v>
+        <v>0.1376243006568773</v>
       </c>
       <c r="P110" t="n">
-        <v>0.1228247019896647</v>
+        <v>0.1228335738595845</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.1084898575685966</v>
+        <v>0.1084976555268877</v>
       </c>
       <c r="R110" t="n">
-        <v>0.1039844744101044</v>
+        <v>0.1039917333492745</v>
       </c>
       <c r="S110" t="n">
-        <v>0.09191075631618177</v>
+        <v>0.09191689566734745</v>
       </c>
       <c r="T110" t="n">
-        <v>0.05953099797344803</v>
+        <v>0.05953469381290077</v>
       </c>
       <c r="U110" t="n">
-        <v>0.02392967640563496</v>
+        <v>0.02393102629035481</v>
       </c>
       <c r="V110" t="n">
-        <v>-0.01155794671932249</v>
+        <v>-0.01155850242100701</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2.325576039619527</v>
+        <v>2.325503823074706</v>
       </c>
       <c r="F111" t="n">
-        <v>2.249059810915147</v>
+        <v>2.249023659309245</v>
       </c>
       <c r="G111" t="n">
-        <v>1.988727683254899</v>
+        <v>1.988706497599706</v>
       </c>
       <c r="H111" t="n">
-        <v>1.676624358217951</v>
+        <v>1.676613511624135</v>
       </c>
       <c r="I111" t="n">
-        <v>1.262342816740824</v>
+        <v>1.262339632978254</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9493725285354232</v>
+        <v>0.9493729257572538</v>
       </c>
       <c r="K111" t="n">
-        <v>0.6989851121985968</v>
+        <v>0.6989860806972875</v>
       </c>
       <c r="L111" t="n">
         <v>0.5443546719993385</v>
       </c>
       <c r="M111" t="n">
-        <v>0.4417011763529772</v>
+        <v>0.4417001208992386</v>
       </c>
       <c r="N111" t="n">
-        <v>0.3689971450288277</v>
+        <v>0.3689953516039666</v>
       </c>
       <c r="O111" t="n">
-        <v>0.3059953134119845</v>
+        <v>0.3059931395176662</v>
       </c>
       <c r="P111" t="n">
-        <v>0.2744408655105569</v>
+        <v>0.2744382668832189</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.2452427868106959</v>
+        <v>0.2452396720524774</v>
       </c>
       <c r="R111" t="n">
-        <v>0.2395943162956274</v>
+        <v>0.2395902544253966</v>
       </c>
       <c r="S111" t="n">
-        <v>0.216973884565996</v>
+        <v>0.2169691808020077</v>
       </c>
       <c r="T111" t="n">
-        <v>0.1430886011698337</v>
+        <v>0.1430850124350832</v>
       </c>
       <c r="U111" t="n">
-        <v>0.0577878794729842</v>
+        <v>0.05778637224106667</v>
       </c>
       <c r="V111" t="n">
-        <v>-0.02787407756876029</v>
+        <v>-0.02787334357216401</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1.408564965886537</v>
+        <v>1.408612667081129</v>
       </c>
       <c r="F112" t="n">
-        <v>1.340140882703966</v>
+        <v>1.340191094643111</v>
       </c>
       <c r="G112" t="n">
-        <v>1.107277934273699</v>
+        <v>1.107342868081138</v>
       </c>
       <c r="H112" t="n">
-        <v>0.8748901747519215</v>
+        <v>0.8749645319722128</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6313339816514133</v>
+        <v>0.631403481465199</v>
       </c>
       <c r="J112" t="n">
-        <v>0.463479371743548</v>
+        <v>0.4635396249470267</v>
       </c>
       <c r="K112" t="n">
-        <v>0.3356422038223306</v>
+        <v>0.3356905854244654</v>
       </c>
       <c r="L112" t="n">
-        <v>0.2571598797745717</v>
+        <v>0.2571992379491632</v>
       </c>
       <c r="M112" t="n">
-        <v>0.2064711585376555</v>
+        <v>0.2065038032890465</v>
       </c>
       <c r="N112" t="n">
-        <v>0.1714961300258476</v>
+        <v>0.1715237862494324</v>
       </c>
       <c r="O112" t="n">
-        <v>0.1419431068873954</v>
+        <v>0.1419663288541053</v>
       </c>
       <c r="P112" t="n">
-        <v>0.126700535413968</v>
+        <v>0.1267215061142742</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.1118228898215644</v>
+        <v>0.1118414773075503</v>
       </c>
       <c r="R112" t="n">
-        <v>0.1068729827943605</v>
+        <v>0.1068906858041338</v>
       </c>
       <c r="S112" t="n">
-        <v>0.09405100363404474</v>
+        <v>0.09406631839973843</v>
       </c>
       <c r="T112" t="n">
-        <v>0.06063643221712655</v>
+        <v>0.06064594675442121</v>
       </c>
       <c r="U112" t="n">
-        <v>0.02425186026927736</v>
+        <v>0.02425541521801224</v>
       </c>
       <c r="V112" t="n">
-        <v>-0.01166045410743163</v>
+        <v>-0.01166198521455625</v>
       </c>
     </row>
     <row r="113">
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1.601896307032642</v>
+        <v>1.635499107517649</v>
       </c>
       <c r="F113" t="n">
-        <v>1.769951162328324</v>
+        <v>1.803178758792428</v>
       </c>
       <c r="G113" t="n">
-        <v>1.431641249337571</v>
+        <v>1.442049125191872</v>
       </c>
       <c r="H113" t="n">
-        <v>1.162081753001064</v>
+        <v>1.154256412562391</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9585355694600768</v>
+        <v>0.9292043614961316</v>
       </c>
       <c r="J113" t="n">
         <v>1.167377084688082</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.8235218301343047</v>
+        <v>0.7362247540442234</v>
       </c>
       <c r="F114" t="n">
-        <v>1.216026819726837</v>
+        <v>1.132697918374553</v>
       </c>
       <c r="G114" t="n">
-        <v>1.380334165559247</v>
+        <v>1.334129045376691</v>
       </c>
       <c r="H114" t="n">
-        <v>1.436607870869928</v>
+        <v>1.41024075753863</v>
       </c>
       <c r="I114" t="n">
-        <v>1.32896300541131</v>
+        <v>1.312870609320375</v>
       </c>
       <c r="J114" t="n">
         <v>1.259513707003369</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.362050196896229</v>
+        <v>1.361548409666827</v>
       </c>
       <c r="F115" t="n">
-        <v>1.739991992140295</v>
+        <v>1.739033697945689</v>
       </c>
       <c r="G115" t="n">
-        <v>1.726175424718997</v>
+        <v>1.727251917963116</v>
       </c>
       <c r="H115" t="n">
-        <v>1.607992438476879</v>
+        <v>1.611517156087891</v>
       </c>
       <c r="I115" t="n">
-        <v>1.381479531951761</v>
+        <v>1.388886049685325</v>
       </c>
       <c r="J115" t="n">
         <v>1.161940480413885</v>
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5.820034517412171</v>
+        <v>5.222726417639647</v>
       </c>
       <c r="F116" t="n">
-        <v>6.863849958932162</v>
+        <v>6.367208347545965</v>
       </c>
       <c r="G116" t="n">
-        <v>6.66853887773891</v>
+        <v>6.264622016721787</v>
       </c>
       <c r="H116" t="n">
-        <v>6.061014749295464</v>
+        <v>5.739957044138126</v>
       </c>
       <c r="I116" t="n">
-        <v>5.113620778693035</v>
+        <v>4.870580920318054</v>
       </c>
       <c r="J116" t="n">
-        <v>4.362255812657703</v>
+        <v>4.172562186084645</v>
       </c>
       <c r="K116" t="n">
-        <v>3.668280818196197</v>
+        <v>3.519930549262963</v>
       </c>
       <c r="L116" t="n">
-        <v>3.130671786664394</v>
+        <v>3.012026624343246</v>
       </c>
       <c r="M116" t="n">
-        <v>2.747433588481373</v>
+        <v>2.64937979601632</v>
       </c>
       <c r="N116" t="n">
-        <v>2.450846763899968</v>
+        <v>2.368262189303629</v>
       </c>
       <c r="O116" t="n">
-        <v>2.170999053640538</v>
+        <v>2.101959000909536</v>
       </c>
       <c r="P116" t="n">
-        <v>1.965906974358698</v>
+        <v>1.907046470402002</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.750696253048014</v>
+        <v>1.701703063838858</v>
       </c>
       <c r="R116" t="n">
-        <v>1.496214033098365</v>
+        <v>1.457445144317031</v>
       </c>
       <c r="S116" t="n">
-        <v>1.273727221101328</v>
+        <v>1.243565581528489</v>
       </c>
       <c r="T116" t="n">
-        <v>1.021226154624068</v>
+        <v>0.9994591936339363</v>
       </c>
       <c r="U116" t="n">
-        <v>0.7177881073860251</v>
+        <v>0.7042932145765722</v>
       </c>
       <c r="V116" t="n">
-        <v>0.4347905921993385</v>
+        <v>0.42782735533567</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1.33890069845126</v>
+        <v>1.382826473456578</v>
       </c>
       <c r="F117" t="n">
-        <v>1.100323173977803</v>
+        <v>1.20555654841648</v>
       </c>
       <c r="G117" t="n">
-        <v>0.901785557376401</v>
+        <v>1.017241038438388</v>
       </c>
       <c r="H117" t="n">
-        <v>0.7386979436685353</v>
+        <v>0.8448668259078866</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5809261156396337</v>
+        <v>0.6672776385443205</v>
       </c>
       <c r="J117" t="n">
-        <v>0.4710881836574463</v>
+        <v>0.5407306207764295</v>
       </c>
       <c r="K117" t="n">
-        <v>0.3814194993132745</v>
+        <v>0.4365525610324414</v>
       </c>
       <c r="L117" t="n">
-        <v>0.3155277781609413</v>
+        <v>0.3597711882920057</v>
       </c>
       <c r="M117" t="n">
-        <v>0.270360356787301</v>
+        <v>0.306791972890726</v>
       </c>
       <c r="N117" t="n">
-        <v>0.2368822404710706</v>
+        <v>0.2673351388872682</v>
       </c>
       <c r="O117" t="n">
-        <v>0.2062210770566502</v>
+        <v>0.2315672171915487</v>
       </c>
       <c r="P117" t="n">
-        <v>0.1829678474834272</v>
+        <v>0.2046049705226823</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.1586235908577972</v>
+        <v>0.1768108458277311</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1312383105876852</v>
+        <v>0.1458614914228937</v>
       </c>
       <c r="S117" t="n">
-        <v>0.1076923228121073</v>
+        <v>0.119289700539894</v>
       </c>
       <c r="T117" t="n">
-        <v>0.08309157375038559</v>
+        <v>0.09161607925657804</v>
       </c>
       <c r="U117" t="n">
-        <v>0.05612959724779058</v>
+        <v>0.06150023445970854</v>
       </c>
       <c r="V117" t="n">
-        <v>0.03251342425430868</v>
+        <v>0.03533053831428559</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.5891723139657621</v>
+        <v>0.6667666046638496</v>
       </c>
       <c r="F118" t="n">
-        <v>0.6106157782298376</v>
+        <v>0.6751914231303625</v>
       </c>
       <c r="G118" t="n">
-        <v>0.5765520891132766</v>
+        <v>0.6289442999646642</v>
       </c>
       <c r="H118" t="n">
-        <v>0.5179696175782471</v>
+        <v>0.5592672855279188</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4334898492558514</v>
+        <v>0.4642208215095806</v>
       </c>
       <c r="J118" t="n">
-        <v>0.367766558026494</v>
+        <v>0.3911265639310138</v>
       </c>
       <c r="K118" t="n">
-        <v>0.3083073675438355</v>
+        <v>0.325993210597106</v>
       </c>
       <c r="L118" t="n">
-        <v>0.2628654755308624</v>
+        <v>0.2765138811278389</v>
       </c>
       <c r="M118" t="n">
-        <v>0.2310612993988794</v>
+        <v>0.2419247198091187</v>
       </c>
       <c r="N118" t="n">
-        <v>0.206420714787202</v>
+        <v>0.2152755953773974</v>
       </c>
       <c r="O118" t="n">
-        <v>0.1821251808740481</v>
+        <v>0.1894040523297617</v>
       </c>
       <c r="P118" t="n">
-        <v>0.1633667210654537</v>
+        <v>0.1695520497667634</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.1430546455888438</v>
+        <v>0.1482705275096724</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1194661828407296</v>
+        <v>0.1236994388251091</v>
       </c>
       <c r="S118" t="n">
-        <v>0.09891181400601699</v>
+        <v>0.1023146037618215</v>
       </c>
       <c r="T118" t="n">
-        <v>0.07696553195571787</v>
+        <v>0.07950545414675543</v>
       </c>
       <c r="U118" t="n">
-        <v>0.05245910408125379</v>
+        <v>0.05408384961251529</v>
       </c>
       <c r="V118" t="n">
-        <v>0.03076261290165849</v>
+        <v>0.03162628650507901</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1.352352430031625</v>
+        <v>1.333369259996954</v>
       </c>
       <c r="F119" t="n">
-        <v>1.202567577995733</v>
+        <v>1.230335900406341</v>
       </c>
       <c r="G119" t="n">
-        <v>0.9459158747626163</v>
+        <v>0.9974035420560573</v>
       </c>
       <c r="H119" t="n">
-        <v>0.7408202109321146</v>
+        <v>0.7979739390832817</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5661697410970327</v>
+        <v>0.6168872108996984</v>
       </c>
       <c r="J119" t="n">
-        <v>0.4528663279239112</v>
+        <v>0.4954906653989508</v>
       </c>
       <c r="K119" t="n">
-        <v>0.365791175697799</v>
+        <v>0.4000508960086137</v>
       </c>
       <c r="L119" t="n">
-        <v>0.3039941549849182</v>
+        <v>0.3315306909301046</v>
       </c>
       <c r="M119" t="n">
-        <v>0.2620858666410098</v>
+        <v>0.2847112491812621</v>
       </c>
       <c r="N119" t="n">
-        <v>0.230588314428504</v>
+        <v>0.2494989048542819</v>
       </c>
       <c r="O119" t="n">
-        <v>0.2008858783095481</v>
+        <v>0.21670268572027</v>
       </c>
       <c r="P119" t="n">
-        <v>0.1785176695806044</v>
+        <v>0.1920732542798868</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.1554576021264221</v>
+        <v>0.1668639989371946</v>
       </c>
       <c r="R119" t="n">
-        <v>0.129374703661056</v>
+        <v>0.1385485106851357</v>
       </c>
       <c r="S119" t="n">
-        <v>0.1067772029938157</v>
+        <v>0.1140655994576904</v>
       </c>
       <c r="T119" t="n">
-        <v>0.08276653435816689</v>
+        <v>0.08814432929211628</v>
       </c>
       <c r="U119" t="n">
-        <v>0.05615211023433764</v>
+        <v>0.05955707994579946</v>
       </c>
       <c r="V119" t="n">
-        <v>0.0327323733928975</v>
+        <v>0.03452594631247258</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8962255890676549</v>
+        <v>0.7962052629110185</v>
       </c>
       <c r="F120" t="n">
-        <v>1.062113337135244</v>
+        <v>0.9788839381617606</v>
       </c>
       <c r="G120" t="n">
-        <v>1.033464422116098</v>
+        <v>0.9656619932442788</v>
       </c>
       <c r="H120" t="n">
-        <v>0.9401996346694705</v>
+        <v>0.8862378432985347</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7937960429703923</v>
+        <v>0.7529309073626099</v>
       </c>
       <c r="J120" t="n">
-        <v>0.6775343317803741</v>
+        <v>0.6456448032782887</v>
       </c>
       <c r="K120" t="n">
-        <v>0.569995331858915</v>
+        <v>0.545068989003084</v>
       </c>
       <c r="L120" t="n">
-        <v>0.4866363993740991</v>
+        <v>0.4667154848804853</v>
       </c>
       <c r="M120" t="n">
-        <v>0.4271981315687038</v>
+        <v>0.4107450369793694</v>
       </c>
       <c r="N120" t="n">
-        <v>0.381184955915551</v>
+        <v>0.3673357028034523</v>
       </c>
       <c r="O120" t="n">
-        <v>0.3377433636157203</v>
+        <v>0.3261704563938461</v>
       </c>
       <c r="P120" t="n">
-        <v>0.3059089207074004</v>
+        <v>0.2960458080528595</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.2724843418063038</v>
+        <v>0.2642769924589933</v>
       </c>
       <c r="R120" t="n">
-        <v>0.2329322235604496</v>
+        <v>0.2264388334480386</v>
       </c>
       <c r="S120" t="n">
-        <v>0.1983471851732013</v>
+        <v>0.1932961860724108</v>
       </c>
       <c r="T120" t="n">
-        <v>0.1590683127506683</v>
+        <v>0.155424754367408</v>
       </c>
       <c r="U120" t="n">
-        <v>0.1118359601807518</v>
+        <v>0.1095765628550031</v>
       </c>
       <c r="V120" t="n">
-        <v>0.06776438939640195</v>
+        <v>0.06659866614358571</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9562223349064843</v>
+        <v>0.849506194634592</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8412835339774094</v>
+        <v>0.775359035016018</v>
       </c>
       <c r="G121" t="n">
-        <v>0.6423559972318108</v>
+        <v>0.6002132815883706</v>
       </c>
       <c r="H121" t="n">
-        <v>0.5014415234805715</v>
+        <v>0.4726622731230579</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3910555436250316</v>
+        <v>0.3709231806534953</v>
       </c>
       <c r="J121" t="n">
-        <v>0.3234104789652237</v>
+        <v>0.308188216522422</v>
       </c>
       <c r="K121" t="n">
-        <v>0.2711606074984751</v>
+        <v>0.259302832107523</v>
       </c>
       <c r="L121" t="n">
-        <v>0.2338999972486544</v>
+        <v>0.2243252050985612</v>
       </c>
       <c r="M121" t="n">
-        <v>0.2080275376872547</v>
+        <v>0.2000158506004</v>
       </c>
       <c r="N121" t="n">
-        <v>0.1874188282613256</v>
+        <v>0.1806095279032915</v>
       </c>
       <c r="O121" t="n">
-        <v>0.1660505221008326</v>
+        <v>0.1603606687351729</v>
       </c>
       <c r="P121" t="n">
-        <v>0.1495058144992167</v>
+        <v>0.1446853787584713</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.1315378554725829</v>
+        <v>0.127575807930287</v>
       </c>
       <c r="R121" t="n">
-        <v>0.110456479329293</v>
+        <v>0.1073774005646172</v>
       </c>
       <c r="S121" t="n">
-        <v>0.09192350877438446</v>
+        <v>0.08958274015439559</v>
       </c>
       <c r="T121" t="n">
-        <v>0.07186630112813129</v>
+        <v>0.07021980638158654</v>
       </c>
       <c r="U121" t="n">
-        <v>0.04922988201709171</v>
+        <v>0.04823543300276571</v>
       </c>
       <c r="V121" t="n">
-        <v>0.02905576572844117</v>
+        <v>0.02855616998213244</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1.18559862893921</v>
+        <v>1.219006874261344</v>
       </c>
       <c r="F122" t="n">
-        <v>1.364071210591672</v>
+        <v>1.383579390158279</v>
       </c>
       <c r="G122" t="n">
-        <v>1.347396726894904</v>
+        <v>1.359356313609128</v>
       </c>
       <c r="H122" t="n">
-        <v>1.238943736707773</v>
+        <v>1.246669264489196</v>
       </c>
       <c r="I122" t="n">
-        <v>1.047321979777792</v>
+        <v>1.052451250093917</v>
       </c>
       <c r="J122" t="n">
-        <v>0.8889180515302511</v>
+        <v>0.8926529133279992</v>
       </c>
       <c r="K122" t="n">
-        <v>0.7409268800480598</v>
+        <v>0.7437651191167043</v>
       </c>
       <c r="L122" t="n">
-        <v>0.6259279429617598</v>
+        <v>0.6281808497802218</v>
       </c>
       <c r="M122" t="n">
-        <v>0.5438545688299714</v>
+        <v>0.5457233241329162</v>
       </c>
       <c r="N122" t="n">
-        <v>0.4809499239315155</v>
+        <v>0.4825312537461305</v>
       </c>
       <c r="O122" t="n">
-        <v>0.4232865747004976</v>
+        <v>0.4245958991152492</v>
       </c>
       <c r="P122" t="n">
-        <v>0.3813765881677093</v>
+        <v>0.382467150115646</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.338412849173147</v>
+        <v>0.3392843417050843</v>
       </c>
       <c r="R122" t="n">
-        <v>0.2884979939837474</v>
+        <v>0.2891496109983287</v>
       </c>
       <c r="S122" t="n">
-        <v>0.2451542412346157</v>
+        <v>0.2456266606374603</v>
       </c>
       <c r="T122" t="n">
-        <v>0.1961951445907718</v>
+        <v>0.1965105081491314</v>
       </c>
       <c r="U122" t="n">
-        <v>0.1375621764331369</v>
+        <v>0.1377425429464318</v>
       </c>
       <c r="V122" t="n">
-        <v>0.08306439257947376</v>
+        <v>0.08314998586200691</v>
       </c>
     </row>
     <row r="123">
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.02866399736620613</v>
+        <v>0.03373417394843086</v>
       </c>
       <c r="F130" t="n">
-        <v>0.03901081995328285</v>
+        <v>0.04301928220178676</v>
       </c>
       <c r="G130" t="n">
-        <v>0.04553715142310043</v>
+        <v>0.0485637819103429</v>
       </c>
       <c r="H130" t="n">
-        <v>0.04248725088716779</v>
+        <v>0.044287613592864</v>
       </c>
       <c r="I130" t="n">
-        <v>0.03464186769808542</v>
+        <v>0.03537833139302655</v>
       </c>
       <c r="J130" t="n">
         <v>0.02719628552819762</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.09423601501060132</v>
+        <v>0.09908285594179862</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1140012606571777</v>
+        <v>0.1182788340578459</v>
       </c>
       <c r="G131" t="n">
-        <v>0.1351117233694646</v>
+        <v>0.1383772779222563</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1330595238559868</v>
+        <v>0.1349758432737795</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1157813452906928</v>
+        <v>0.1165503517765924</v>
       </c>
       <c r="J131" t="n">
         <v>0.09639129754821993</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.5870868360889538</v>
+        <v>0.5885224923750756</v>
       </c>
       <c r="F132" t="n">
-        <v>0.9487397412904538</v>
+        <v>0.9496178249002369</v>
       </c>
       <c r="G132" t="n">
-        <v>1.308268517065704</v>
+        <v>1.308678471582539</v>
       </c>
       <c r="H132" t="n">
-        <v>1.433669703886466</v>
+        <v>1.433808075891258</v>
       </c>
       <c r="I132" t="n">
-        <v>1.340378157126837</v>
+        <v>1.340406401569777</v>
       </c>
       <c r="J132" t="n">
         <v>1.161656288789396</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2.609333015927505</v>
+        <v>2.608033446775853</v>
       </c>
       <c r="F133" t="n">
-        <v>2.363068404677223</v>
+        <v>2.362391899368829</v>
       </c>
       <c r="G133" t="n">
-        <v>1.95888804904435</v>
+        <v>1.958687360858429</v>
       </c>
       <c r="H133" t="n">
-        <v>1.575140010131095</v>
+        <v>1.575147884226844</v>
       </c>
       <c r="I133" t="n">
-        <v>1.265258875162947</v>
+        <v>1.265281202819535</v>
       </c>
       <c r="J133" t="n">
         <v>1.05377332515359</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.1153941396360822</v>
+        <v>0.1172686424120809</v>
       </c>
       <c r="F134" t="n">
-        <v>0.2342252289257932</v>
+        <v>0.2354597123078827</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3706297779528</v>
+        <v>0.3713817428889647</v>
       </c>
       <c r="H134" t="n">
-        <v>0.4301982338685874</v>
+        <v>0.4305747165334642</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4081091321135095</v>
+        <v>0.408246322641812</v>
       </c>
       <c r="J134" t="n">
         <v>0.3543721254610276</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3.183038900841757</v>
+        <v>3.181217562835739</v>
       </c>
       <c r="F135" t="n">
-        <v>3.573766869830616</v>
+        <v>3.572156756364001</v>
       </c>
       <c r="G135" t="n">
-        <v>3.390986297700239</v>
+        <v>3.389883732452878</v>
       </c>
       <c r="H135" t="n">
-        <v>2.871215385974844</v>
+        <v>2.870681700994639</v>
       </c>
       <c r="I135" t="n">
-        <v>2.266517234910578</v>
+        <v>2.266336566833163</v>
       </c>
       <c r="J135" t="n">
         <v>1.764250992701675</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.04157402932427642</v>
+        <v>0.04870638126736408</v>
       </c>
       <c r="F136" t="n">
-        <v>0.07232849119340376</v>
+        <v>0.07725803335404324</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1292819143301914</v>
+        <v>0.1323215505845857</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1907310143656842</v>
+        <v>0.1921895022593917</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2242696445935924</v>
+        <v>0.2247702750452422</v>
       </c>
       <c r="J136" t="n">
         <v>0.2086564727498343</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.3223207098424546</v>
+        <v>0.3235234877770922</v>
       </c>
       <c r="F137" t="n">
-        <v>0.4621409666546302</v>
+        <v>0.4630508057527947</v>
       </c>
       <c r="G137" t="n">
-        <v>0.6267067379769243</v>
+        <v>0.6272671197052232</v>
       </c>
       <c r="H137" t="n">
-        <v>0.6868708897093271</v>
+        <v>0.6871426886825263</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6212573708838222</v>
+        <v>0.6213574086687944</v>
       </c>
       <c r="J137" t="n">
         <v>0.5093848436616611</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.15546396423987</v>
+        <v>0.1615969819651606</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2553195259150282</v>
+        <v>0.2599634764683492</v>
       </c>
       <c r="G138" t="n">
-        <v>0.3719820960884342</v>
+        <v>0.3751669539468184</v>
       </c>
       <c r="H138" t="n">
-        <v>0.4461118458478801</v>
+        <v>0.4477909658756955</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4670393269674677</v>
+        <v>0.467644329522838</v>
       </c>
       <c r="J138" t="n">
         <v>0.4542443167698482</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.653674890569906</v>
+        <v>0.6650158868717362</v>
       </c>
       <c r="F139" t="n">
-        <v>1.025369072223301</v>
+        <v>1.034096385258022</v>
       </c>
       <c r="G139" t="n">
-        <v>1.274596772012326</v>
+        <v>1.281046977300225</v>
       </c>
       <c r="H139" t="n">
-        <v>1.237527973683805</v>
+        <v>1.241348001669211</v>
       </c>
       <c r="I139" t="n">
-        <v>1.04353664654298</v>
+        <v>1.045101915231732</v>
       </c>
       <c r="J139" t="n">
         <v>0.8465032604507974</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.1664150287807832</v>
+        <v>0.1709657231765692</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3330708218038877</v>
+        <v>0.3361616800134236</v>
       </c>
       <c r="G140" t="n">
-        <v>0.5220287137620061</v>
+        <v>0.5240146365457388</v>
       </c>
       <c r="H140" t="n">
-        <v>0.5924361207501426</v>
+        <v>0.5934925843919584</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5330268174973715</v>
+        <v>0.5334407473416015</v>
       </c>
       <c r="J140" t="n">
         <v>0.4298136062770478</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5.411175543902711</v>
+        <v>5.406880240990739</v>
       </c>
       <c r="F141" t="n">
-        <v>8.037472626608903</v>
+        <v>8.032275645639009</v>
       </c>
       <c r="G141" t="n">
-        <v>9.845015344211987</v>
+        <v>9.840002286877748</v>
       </c>
       <c r="H141" t="n">
-        <v>9.756583162303553</v>
+        <v>9.753402480640238</v>
       </c>
       <c r="I141" t="n">
-        <v>8.394556261674779</v>
+        <v>8.393253615204259</v>
       </c>
       <c r="J141" t="n">
         <v>6.892159785289136</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>10.39805019505889</v>
+        <v>10.38939152602044</v>
       </c>
       <c r="F142" t="n">
-        <v>6.253075165912292</v>
+        <v>6.249005806663442</v>
       </c>
       <c r="G142" t="n">
-        <v>2.918225707892573</v>
+        <v>2.916861562685214</v>
       </c>
       <c r="H142" t="n">
-        <v>1.505597665236994</v>
+        <v>1.505226903773397</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9069550393136222</v>
+        <v>0.9068742457176162</v>
       </c>
       <c r="J142" t="n">
         <v>0.6443439730376642</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>9.298584777319633</v>
+        <v>9.288235131749648</v>
       </c>
       <c r="F146" t="n">
-        <v>14.72160420402756</v>
+        <v>14.70953115930901</v>
       </c>
       <c r="G146" t="n">
-        <v>19.74014483917808</v>
+        <v>19.72634598910391</v>
       </c>
       <c r="H146" t="n">
-        <v>20.12564653133312</v>
+        <v>20.11532699767669</v>
       </c>
       <c r="I146" t="n">
-        <v>16.4677599816694</v>
+        <v>16.46333544599775</v>
       </c>
       <c r="J146" t="n">
         <v>11.86292653278922</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.7031060491033454</v>
+        <v>0.703887180481594</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8294226071312032</v>
+        <v>0.8301087407067704</v>
       </c>
       <c r="G147" t="n">
-        <v>0.8841793303702891</v>
+        <v>0.8846946672054018</v>
       </c>
       <c r="H147" t="n">
-        <v>0.849962620143552</v>
+        <v>0.8502509311439577</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7341859335824075</v>
+        <v>0.7342949448502085</v>
       </c>
       <c r="J147" t="n">
         <v>0.5916344389092816</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1.333903587035132</v>
+        <v>1.33414302927556</v>
       </c>
       <c r="F148" t="n">
-        <v>1.54381562706331</v>
+        <v>1.544084479310112</v>
       </c>
       <c r="G148" t="n">
-        <v>1.490635092517893</v>
+        <v>1.490931736506279</v>
       </c>
       <c r="H148" t="n">
-        <v>1.316818043142918</v>
+        <v>1.317030524324006</v>
       </c>
       <c r="I148" t="n">
-        <v>1.099090530339308</v>
+        <v>1.09917731640321</v>
       </c>
       <c r="J148" t="n">
         <v>0.8891831836307182</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2.044613155224355</v>
+        <v>2.038565331066356</v>
       </c>
       <c r="F149" t="n">
-        <v>2.347138651915521</v>
+        <v>2.34358226606051</v>
       </c>
       <c r="G149" t="n">
-        <v>2.393737311031366</v>
+        <v>2.391617124921213</v>
       </c>
       <c r="H149" t="n">
-        <v>2.201582546703432</v>
+        <v>2.200467236475614</v>
       </c>
       <c r="I149" t="n">
-        <v>1.691219619894464</v>
+        <v>1.690819114224245</v>
       </c>
       <c r="J149" t="n">
         <v>1.198466075856321</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.16007880949977</v>
+        <v>0.1649169835874308</v>
       </c>
       <c r="F150" t="n">
-        <v>0.1669077908626107</v>
+        <v>0.1694779695485398</v>
       </c>
       <c r="G150" t="n">
-        <v>0.1578276369672791</v>
+        <v>0.1592775122547725</v>
       </c>
       <c r="H150" t="n">
-        <v>0.145395553253472</v>
+        <v>0.146162541514057</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1156689749148216</v>
+        <v>0.1159627768651774</v>
       </c>
       <c r="J150" t="n">
         <v>0.08565369717777732</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.6218773293889823</v>
+        <v>0.6225602600157645</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6347675458340029</v>
+        <v>0.6352200903003757</v>
       </c>
       <c r="G151" t="n">
-        <v>0.5767543787719759</v>
+        <v>0.5770813223938225</v>
       </c>
       <c r="H151" t="n">
-        <v>0.5103701995130189</v>
+        <v>0.5105680674017177</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4076855420382015</v>
+        <v>0.4077618966733236</v>
       </c>
       <c r="J151" t="n">
         <v>0.3128319325061372</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.3539899833275732</v>
+        <v>0.3546717487941732</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3085569866548231</v>
+        <v>0.3091619193008699</v>
       </c>
       <c r="G152" t="n">
-        <v>0.2759043204258284</v>
+        <v>0.2762941505087469</v>
       </c>
       <c r="H152" t="n">
-        <v>0.254839511451765</v>
+        <v>0.2550457676519406</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2146931121306208</v>
+        <v>0.214765435531458</v>
       </c>
       <c r="J152" t="n">
         <v>0.1705597687935742</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2.34328282146723</v>
+        <v>2.334985175555924</v>
       </c>
       <c r="F153" t="n">
-        <v>2.661382000374725</v>
+        <v>2.656667151450355</v>
       </c>
       <c r="G153" t="n">
-        <v>2.523555467967208</v>
+        <v>2.521006719779626</v>
       </c>
       <c r="H153" t="n">
-        <v>2.178666471655235</v>
+        <v>2.177421806679344</v>
       </c>
       <c r="I153" t="n">
-        <v>1.62337293401839</v>
+        <v>1.622938283307707</v>
       </c>
       <c r="J153" t="n">
         <v>1.138916393023739</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.152401833001097</v>
+        <v>0.1541404711072318</v>
       </c>
       <c r="F154" t="n">
-        <v>0.1290987972114231</v>
+        <v>0.1302196069015276</v>
       </c>
       <c r="G154" t="n">
-        <v>0.1092238546203964</v>
+        <v>0.1099146573827812</v>
       </c>
       <c r="H154" t="n">
-        <v>0.09550914655745688</v>
+        <v>0.09588897561056926</v>
       </c>
       <c r="I154" t="n">
-        <v>0.07761028420208559</v>
+        <v>0.07775388460199459</v>
       </c>
       <c r="J154" t="n">
         <v>0.06096292346674575</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.4274540961334206</v>
+        <v>0.4268543796266839</v>
       </c>
       <c r="F155" t="n">
-        <v>0.5083750284257404</v>
+        <v>0.5080031981061365</v>
       </c>
       <c r="G155" t="n">
-        <v>0.4769301651116953</v>
+        <v>0.4767312087577454</v>
       </c>
       <c r="H155" t="n">
-        <v>0.4262027157131693</v>
+        <v>0.4261033559310356</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3549353671044703</v>
+        <v>0.3548978844150713</v>
       </c>
       <c r="J155" t="n">
         <v>0.289567545737397</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.09773187214541799</v>
+        <v>0.09783763754585395</v>
       </c>
       <c r="F156" t="n">
-        <v>0.108557294984538</v>
+        <v>0.1086347943560492</v>
       </c>
       <c r="G156" t="n">
-        <v>0.09643570687755425</v>
+        <v>0.09648267536854439</v>
       </c>
       <c r="H156" t="n">
-        <v>0.08361784288456564</v>
+        <v>0.08364392115838695</v>
       </c>
       <c r="I156" t="n">
-        <v>0.06862544451374454</v>
+        <v>0.06863627187041459</v>
       </c>
       <c r="J156" t="n">
         <v>0.05522255207814827</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.003732917105499107</v>
+        <v>0.004538600838012108</v>
       </c>
       <c r="F157" t="n">
-        <v>0.002562090161783691</v>
+        <v>0.003192991744635296</v>
       </c>
       <c r="G157" t="n">
-        <v>0.001520816447477362</v>
+        <v>0.001932613451163926</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0010460240276661</v>
+        <v>0.00127973215195764</v>
       </c>
       <c r="I157" t="n">
-        <v>0.000789393686811732</v>
+        <v>0.0008825519479882717</v>
       </c>
       <c r="J157" t="n">
         <v>0.000649925366746959</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.008232216749225002</v>
+        <v>0.008668115492083205</v>
       </c>
       <c r="F158" t="n">
-        <v>0.01149185401555085</v>
+        <v>0.01174286558174343</v>
       </c>
       <c r="G158" t="n">
-        <v>0.01320991732877113</v>
+        <v>0.01333298762189122</v>
       </c>
       <c r="H158" t="n">
-        <v>0.01372314738754885</v>
+        <v>0.01378204444349617</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0124803234544423</v>
+        <v>0.01250256361084254</v>
       </c>
       <c r="J158" t="n">
         <v>0.01057442830715067</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.006290575396531443</v>
+        <v>0.0085987987756638</v>
       </c>
       <c r="F159" t="n">
-        <v>0.007282508307918959</v>
+        <v>0.008683205308139388</v>
       </c>
       <c r="G159" t="n">
-        <v>0.006766935271753425</v>
+        <v>0.007513503317046991</v>
       </c>
       <c r="H159" t="n">
-        <v>0.00614562047720743</v>
+        <v>0.006524600406635221</v>
       </c>
       <c r="I159" t="n">
-        <v>0.005196814743132071</v>
+        <v>0.005343589309836136</v>
       </c>
       <c r="J159" t="n">
         <v>0.004320174265667621</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.1692954611114784</v>
+        <v>0.1691216048750991</v>
       </c>
       <c r="F160" t="n">
-        <v>0.1974380764755968</v>
+        <v>0.1973343689590576</v>
       </c>
       <c r="G160" t="n">
-        <v>0.1682764409335897</v>
+        <v>0.1682310405352965</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1351445945721256</v>
+        <v>0.1351274058089481</v>
       </c>
       <c r="I160" t="n">
-        <v>0.102778823140734</v>
+        <v>0.1027741034822385</v>
       </c>
       <c r="J160" t="n">
         <v>0.08033396892825824</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.001938486301130201</v>
+        <v>0.003179490768279739</v>
       </c>
       <c r="F162" t="n">
-        <v>0.004343754533903708</v>
+        <v>0.004990041898765899</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0107277672049393</v>
+        <v>0.01106065459478812</v>
       </c>
       <c r="H162" t="n">
-        <v>0.01971677164814882</v>
+        <v>0.01988200162005973</v>
       </c>
       <c r="I162" t="n">
-        <v>0.02509285332104402</v>
+        <v>0.02515338860921152</v>
       </c>
       <c r="J162" t="n">
         <v>0.02519883800175899</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.2010213330285704</v>
+        <v>0.201108462037212</v>
       </c>
       <c r="F163" t="n">
-        <v>0.1832092818394188</v>
+        <v>0.1832973723384682</v>
       </c>
       <c r="G163" t="n">
-        <v>0.1281766520034161</v>
+        <v>0.1282621660371575</v>
       </c>
       <c r="H163" t="n">
-        <v>0.09654882004449965</v>
+        <v>0.0966113697491757</v>
       </c>
       <c r="I163" t="n">
-        <v>0.07326795181922478</v>
+        <v>0.07329736897485738</v>
       </c>
       <c r="J163" t="n">
         <v>0.05771556778416907</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1.228116949903585</v>
+        <v>1.227888955589553</v>
       </c>
       <c r="F164" t="n">
-        <v>0.9417453855888541</v>
+        <v>0.9416353554072814</v>
       </c>
       <c r="G164" t="n">
-        <v>0.5929279624149515</v>
+        <v>0.5928893633446413</v>
       </c>
       <c r="H164" t="n">
-        <v>0.3925377654324168</v>
+        <v>0.3925293462369023</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2587479933788532</v>
+        <v>0.2587483683022282</v>
       </c>
       <c r="J164" t="n">
         <v>0.1787578106865396</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.4828366410239835</v>
+        <v>0.4828273416828418</v>
       </c>
       <c r="F165" t="n">
-        <v>0.5519127426232516</v>
+        <v>0.5519036880224766</v>
       </c>
       <c r="G165" t="n">
-        <v>0.6846441759597105</v>
+        <v>0.6846132312904695</v>
       </c>
       <c r="H165" t="n">
-        <v>0.7842733038747843</v>
+        <v>0.7842365613179997</v>
       </c>
       <c r="I165" t="n">
-        <v>0.7565169429670248</v>
+        <v>0.7564945493768167</v>
       </c>
       <c r="J165" t="n">
         <v>0.6680862758332689</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4.045659250174085</v>
+        <v>4.044799986608138</v>
       </c>
       <c r="F166" t="n">
-        <v>4.759927375168149</v>
+        <v>4.759195534443888</v>
       </c>
       <c r="G166" t="n">
-        <v>4.670108400519656</v>
+        <v>4.66954096777139</v>
       </c>
       <c r="H166" t="n">
-        <v>4.343017735572342</v>
+        <v>4.342643649248781</v>
       </c>
       <c r="I166" t="n">
-        <v>3.659027673558208</v>
+        <v>3.658858226132178</v>
       </c>
       <c r="J166" t="n">
         <v>2.958500358577032</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.0204435328032128</v>
+        <v>0.02103716134293568</v>
       </c>
       <c r="F167" t="n">
-        <v>0.03023053915469489</v>
+        <v>0.03066311665163958</v>
       </c>
       <c r="G167" t="n">
-        <v>0.03534101216363933</v>
+        <v>0.03564853361862456</v>
       </c>
       <c r="H167" t="n">
-        <v>0.03559025374230564</v>
+        <v>0.03578354758842783</v>
       </c>
       <c r="I167" t="n">
-        <v>0.03030802822451352</v>
+        <v>0.03039214136794224</v>
       </c>
       <c r="J167" t="n">
         <v>0.02410596233370169</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.1070860300799288</v>
+        <v>0.1082691986721807</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1256765134048911</v>
+        <v>0.1266238063064632</v>
       </c>
       <c r="G168" t="n">
-        <v>0.1231571163533847</v>
+        <v>0.1238800747387116</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1143879620212383</v>
+        <v>0.1148585903890739</v>
       </c>
       <c r="I168" t="n">
-        <v>0.09623729978438904</v>
+        <v>0.09644105062448112</v>
       </c>
       <c r="J168" t="n">
         <v>0.07769212415422365</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.6371217730270416</v>
+        <v>0.6370620608497389</v>
       </c>
       <c r="F169" t="n">
-        <v>0.8542657844672831</v>
+        <v>0.85419139471181</v>
       </c>
       <c r="G169" t="n">
-        <v>0.9602609082770167</v>
+        <v>0.9601849075503165</v>
       </c>
       <c r="H169" t="n">
-        <v>0.9321355451001561</v>
+        <v>0.932081107833433</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7506940699391303</v>
+        <v>0.7506708844962512</v>
       </c>
       <c r="J169" t="n">
         <v>0.5575691395500284</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.4360418601408683</v>
+        <v>0.4360029840986445</v>
       </c>
       <c r="F170" t="n">
-        <v>0.3274906739640778</v>
+        <v>0.3274929436538757</v>
       </c>
       <c r="G170" t="n">
-        <v>0.2366799179033992</v>
+        <v>0.2366967802127436</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1910812640250899</v>
+        <v>0.1910962174750003</v>
       </c>
       <c r="I170" t="n">
-        <v>0.152916375286261</v>
+        <v>0.1529233037503314</v>
       </c>
       <c r="J170" t="n">
         <v>0.1238512464425641</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.1063091770287826</v>
+        <v>0.1063812747621622</v>
       </c>
       <c r="F171" t="n">
-        <v>0.1250533680458128</v>
+        <v>0.1251100441930464</v>
       </c>
       <c r="G171" t="n">
-        <v>0.1226821082430185</v>
+        <v>0.122725165976461</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1140781535803639</v>
+        <v>0.1141060186576596</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0961010980939203</v>
+        <v>0.09611313895068163</v>
       </c>
       <c r="J171" t="n">
         <v>0.07769304541199751</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.0009510719467878602</v>
+        <v>0.001674307470694631</v>
       </c>
       <c r="F172" t="n">
-        <v>0.0009932070820074905</v>
+        <v>0.001539444622775453</v>
       </c>
       <c r="G172" t="n">
-        <v>0.00102066382483849</v>
+        <v>0.001402899690876363</v>
       </c>
       <c r="H172" t="n">
-        <v>0.001018511317768005</v>
+        <v>0.001248303526407289</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0008897989648962235</v>
+        <v>0.0009853985583187087</v>
       </c>
       <c r="J172" t="n">
         <v>0.0007241423277087936</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1.127581540327991</v>
+        <v>1.127373846765008</v>
       </c>
       <c r="F173" t="n">
-        <v>1.002049476212226</v>
+        <v>1.001927185395824</v>
       </c>
       <c r="G173" t="n">
-        <v>0.8135308669501468</v>
+        <v>0.8134592006285402</v>
       </c>
       <c r="H173" t="n">
-        <v>0.7061847598536261</v>
+        <v>0.7061413969130405</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5780215049015279</v>
+        <v>0.5780027377903383</v>
       </c>
       <c r="J173" t="n">
         <v>0.466423757831666</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.0453192383380039</v>
+        <v>0.04559421450593727</v>
       </c>
       <c r="F174" t="n">
-        <v>0.06104946846216208</v>
+        <v>0.06125645474383805</v>
       </c>
       <c r="G174" t="n">
-        <v>0.06721995307561145</v>
+        <v>0.06736985270910191</v>
       </c>
       <c r="H174" t="n">
-        <v>0.06563562682303289</v>
+        <v>0.06573077600291548</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0546989004805153</v>
+        <v>0.05474065282289712</v>
       </c>
       <c r="J174" t="n">
         <v>0.04084700087180811</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>3.629910587308069</v>
+        <v>3.629153431670875</v>
       </c>
       <c r="F175" t="n">
-        <v>2.145432146473693</v>
+        <v>2.145133856668576</v>
       </c>
       <c r="G175" t="n">
-        <v>1.185100407870759</v>
+        <v>1.184991408466497</v>
       </c>
       <c r="H175" t="n">
-        <v>0.7374383066088694</v>
+        <v>0.7374030052133997</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4515383709551016</v>
+        <v>0.451531772425863</v>
       </c>
       <c r="J175" t="n">
         <v>0.2877320359698728</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.05255418391622801</v>
+        <v>0.05263848041511342</v>
       </c>
       <c r="F176" t="n">
-        <v>0.08460426158841022</v>
+        <v>0.08464973308233069</v>
       </c>
       <c r="G176" t="n">
-        <v>0.09955981471476524</v>
+        <v>0.09959524210190689</v>
       </c>
       <c r="H176" t="n">
-        <v>0.09875593952483801</v>
+        <v>0.09877321814254859</v>
       </c>
       <c r="I176" t="n">
-        <v>0.08083806938671644</v>
+        <v>0.08084655187038765</v>
       </c>
       <c r="J176" t="n">
         <v>0.06209972169131207</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.2925453979111342</v>
+        <v>0.2926387901976465</v>
       </c>
       <c r="F177" t="n">
-        <v>0.1812848889551499</v>
+        <v>0.181417799759386</v>
       </c>
       <c r="G177" t="n">
-        <v>0.1095769906809457</v>
+        <v>0.1097120666241083</v>
       </c>
       <c r="H177" t="n">
-        <v>0.07851513223373006</v>
+        <v>0.07861506255476756</v>
       </c>
       <c r="I177" t="n">
-        <v>0.05996402260251138</v>
+        <v>0.06000973586213233</v>
       </c>
       <c r="J177" t="n">
         <v>0.04824424054986334</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.06838806737146283</v>
+        <v>0.06841413415456113</v>
       </c>
       <c r="F178" t="n">
-        <v>0.07670801443946966</v>
+        <v>0.07673136848005231</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0759670004332547</v>
+        <v>0.07598204399942232</v>
       </c>
       <c r="H178" t="n">
-        <v>0.07202610485120618</v>
+        <v>0.07203703653094076</v>
       </c>
       <c r="I178" t="n">
-        <v>0.06161192113433345</v>
+        <v>0.06161693675800118</v>
       </c>
       <c r="J178" t="n">
         <v>0.05043667209895115</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.07230201288027809</v>
+        <v>0.07241518687181697</v>
       </c>
       <c r="F179" t="n">
-        <v>0.08983896838461863</v>
+        <v>0.08992338862859313</v>
       </c>
       <c r="G179" t="n">
-        <v>0.08597603581687846</v>
+        <v>0.08604332186020031</v>
       </c>
       <c r="H179" t="n">
-        <v>0.07669218146423001</v>
+        <v>0.07673804694586854</v>
       </c>
       <c r="I179" t="n">
-        <v>0.06017460092661905</v>
+        <v>0.06019483278370122</v>
       </c>
       <c r="J179" t="n">
         <v>0.04446995054961724</v>
